--- a/assets/ASIENTOS_CONTABLES_CABECERA3.xlsx
+++ b/assets/ASIENTOS_CONTABLES_CABECERA3.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://llamgas-my.sharepoint.com/personal/analista_proyectos_grupollamagas_pe/Documents/Documentos/GitHub/Jobs_JE/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{60D0A534-DD33-4DFF-A792-46480B940D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C30543E3-6224-478F-9E9A-2C2A85F2EDFA}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{60D0A534-DD33-4DFF-A792-46480B940D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17C4CA1C-3CAE-4078-AAA3-E6DC818CE04B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CabeceraSaldosBancosFinal" sheetId="4" r:id="rId1"/>
-    <sheet name="Cabecera_Saldos_Bancos" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Hoja1" sheetId="5" r:id="rId2"/>
+    <sheet name="Cabecera_Saldos_Bancos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Cabecera_Saldos_Bancos!$A$2:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Cabecera_Saldos_Bancos!$A$2:$Q$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CabeceraSaldosBancosFinal!$A$2:$I$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="510">
   <si>
     <t>JdtNum</t>
   </si>
@@ -134,6 +135,1443 @@
   </si>
   <si>
     <t>20251231</t>
+  </si>
+  <si>
+    <t>Reconciliado</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Info.detallada</t>
+  </si>
+  <si>
+    <t>Info detallada 2</t>
+  </si>
+  <si>
+    <t>Importe débito</t>
+  </si>
+  <si>
+    <t>Importe del Crédito</t>
+  </si>
+  <si>
+    <t>Saldo actual</t>
+  </si>
+  <si>
+    <t>Crear pago</t>
+  </si>
+  <si>
+    <t>Nº documento</t>
+  </si>
+  <si>
+    <t>Código SN</t>
+  </si>
+  <si>
+    <t>Nombre SN</t>
+  </si>
+  <si>
+    <t>Código externo</t>
+  </si>
+  <si>
+    <t>Número de estado de cuenta</t>
+  </si>
+  <si>
+    <t>Tipo transac.</t>
+  </si>
+  <si>
+    <t>Saldo inicial</t>
+  </si>
+  <si>
+    <t>SOL 109,522,649.69</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>*A/TRANSFER. GRUPO DE GESTIO</t>
+  </si>
+  <si>
+    <t>SOL 46,779.79</t>
+  </si>
+  <si>
+    <t>SOL 109,569,429.48</t>
+  </si>
+  <si>
+    <t>Doc Num</t>
+  </si>
+  <si>
+    <t>10464047633ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 40,000.00</t>
+  </si>
+  <si>
+    <t>SOL 109,609,429.48</t>
+  </si>
+  <si>
+    <t>C10464047633</t>
+  </si>
+  <si>
+    <t>10414056496ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 500.00</t>
+  </si>
+  <si>
+    <t>SOL 109,609,929.48</t>
+  </si>
+  <si>
+    <t>C10414056496</t>
+  </si>
+  <si>
+    <t>PAGO CANALIZA</t>
+  </si>
+  <si>
+    <t>SOL 22,881.84</t>
+  </si>
+  <si>
+    <t>SOL 109,632,811.32</t>
+  </si>
+  <si>
+    <t>R20100154308SAN FERNANDO SA</t>
+  </si>
+  <si>
+    <t>SOL 12,811.26</t>
+  </si>
+  <si>
+    <t>SOL 109,645,622.58</t>
+  </si>
+  <si>
+    <t>ESTACION DE SERVICIOS SIU SA</t>
+  </si>
+  <si>
+    <t>SOL 11,193.48</t>
+  </si>
+  <si>
+    <t>SOL 109,656,816.06</t>
+  </si>
+  <si>
+    <t>10448025506ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 10,000.00</t>
+  </si>
+  <si>
+    <t>SOL 109,666,816.06</t>
+  </si>
+  <si>
+    <t>C10448025506</t>
+  </si>
+  <si>
+    <t>93150000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,667,316.06</t>
+  </si>
+  <si>
+    <t>ZN03.11</t>
+  </si>
+  <si>
+    <t>20498402331ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 7,937.14</t>
+  </si>
+  <si>
+    <t>SOL 109,675,253.20</t>
+  </si>
+  <si>
+    <t>C20498402331</t>
+  </si>
+  <si>
+    <t>93030000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,675,753.20</t>
+  </si>
+  <si>
+    <t>ZN03.01</t>
+  </si>
+  <si>
+    <t>*43100000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 7,090.00</t>
+  </si>
+  <si>
+    <t>SOL 109,682,843.20</t>
+  </si>
+  <si>
+    <t>ZN04.03</t>
+  </si>
+  <si>
+    <t>43010000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,683,343.20</t>
+  </si>
+  <si>
+    <t>PL04</t>
+  </si>
+  <si>
+    <t>R20615032299MULTISERVICIOS C</t>
+  </si>
+  <si>
+    <t>SOL 6,619.80</t>
+  </si>
+  <si>
+    <t>SOL 109,689,963.00</t>
+  </si>
+  <si>
+    <t>*20603091460ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 6,103.68</t>
+  </si>
+  <si>
+    <t>SOL 109,696,066.68</t>
+  </si>
+  <si>
+    <t>SOL 5,000.00</t>
+  </si>
+  <si>
+    <t>SOL 109,701,066.68</t>
+  </si>
+  <si>
+    <t>10304301843ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 4,072.90</t>
+  </si>
+  <si>
+    <t>SOL 109,705,139.58</t>
+  </si>
+  <si>
+    <t>C10304301843</t>
+  </si>
+  <si>
+    <t>93080000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 3,162.40</t>
+  </si>
+  <si>
+    <t>SOL 109,708,301.98</t>
+  </si>
+  <si>
+    <t>ZN03.06</t>
+  </si>
+  <si>
+    <t>33030000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 3,000.00</t>
+  </si>
+  <si>
+    <t>SOL 109,711,301.98</t>
+  </si>
+  <si>
+    <t>ZN02.03</t>
+  </si>
+  <si>
+    <t>72090000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,711,801.98</t>
+  </si>
+  <si>
+    <t>ZN01.06</t>
+  </si>
+  <si>
+    <t>*20534538724ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,714,801.98</t>
+  </si>
+  <si>
+    <t>SOL 2,696.06</t>
+  </si>
+  <si>
+    <t>SOL 109,717,498.04</t>
+  </si>
+  <si>
+    <t>43100000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,717,998.04</t>
+  </si>
+  <si>
+    <t>*53010000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 2,682.00</t>
+  </si>
+  <si>
+    <t>SOL 109,720,680.04</t>
+  </si>
+  <si>
+    <t>PL06</t>
+  </si>
+  <si>
+    <t>93250000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,721,180.04</t>
+  </si>
+  <si>
+    <t>ZN03.15</t>
+  </si>
+  <si>
+    <t>33070000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 2,314.00</t>
+  </si>
+  <si>
+    <t>SOL 109,723,494.04</t>
+  </si>
+  <si>
+    <t>ZN02.07</t>
+  </si>
+  <si>
+    <t>*10457250661ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 2,164.63</t>
+  </si>
+  <si>
+    <t>SOL 109,725,658.67</t>
+  </si>
+  <si>
+    <t>63070000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,726,158.67</t>
+  </si>
+  <si>
+    <t>ZN07.04</t>
+  </si>
+  <si>
+    <t>*82010000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 2,125.09</t>
+  </si>
+  <si>
+    <t>SOL 109,728,283.76</t>
+  </si>
+  <si>
+    <t>PL05</t>
+  </si>
+  <si>
+    <t>43060000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,728,783.76</t>
+  </si>
+  <si>
+    <t>ZN04.07</t>
+  </si>
+  <si>
+    <t>*63030000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 2,000.00</t>
+  </si>
+  <si>
+    <t>SOL 109,730,783.76</t>
+  </si>
+  <si>
+    <t>ZN07.02</t>
+  </si>
+  <si>
+    <t>20564026086ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 1,900.00</t>
+  </si>
+  <si>
+    <t>SOL 109,732,683.76</t>
+  </si>
+  <si>
+    <t>C20564026086</t>
+  </si>
+  <si>
+    <t>R20381235051NEWREST PERU S A</t>
+  </si>
+  <si>
+    <t>SOL 1,800.02</t>
+  </si>
+  <si>
+    <t>SOL 109,734,483.78</t>
+  </si>
+  <si>
+    <t>R20341198217COMPAÑIA PERUANA</t>
+  </si>
+  <si>
+    <t>SOL 1,436.02</t>
+  </si>
+  <si>
+    <t>SOL 109,735,919.80</t>
+  </si>
+  <si>
+    <t>93010000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,736,419.80</t>
+  </si>
+  <si>
+    <t>PL03</t>
+  </si>
+  <si>
+    <t>SOL 1,348.26</t>
+  </si>
+  <si>
+    <t>SOL 109,737,768.06</t>
+  </si>
+  <si>
+    <t>93140000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 1,290.00</t>
+  </si>
+  <si>
+    <t>SOL 109,739,058.06</t>
+  </si>
+  <si>
+    <t>ZN03.10</t>
+  </si>
+  <si>
+    <t>*20606635282ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 1,276.00</t>
+  </si>
+  <si>
+    <t>SOL 109,740,334.06</t>
+  </si>
+  <si>
+    <t>33050000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,740,834.06</t>
+  </si>
+  <si>
+    <t>ZN02.04</t>
+  </si>
+  <si>
+    <t>SOL 1,100.00</t>
+  </si>
+  <si>
+    <t>SOL 109,741,934.06</t>
+  </si>
+  <si>
+    <t>SOL 1,022.50</t>
+  </si>
+  <si>
+    <t>SOL 109,742,956.56</t>
+  </si>
+  <si>
+    <t>93070000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,743,456.56</t>
+  </si>
+  <si>
+    <t>ZN03.05</t>
+  </si>
+  <si>
+    <t>SOL 1,000.00</t>
+  </si>
+  <si>
+    <t>SOL 109,744,456.56</t>
+  </si>
+  <si>
+    <t>43080000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,744,956.56</t>
+  </si>
+  <si>
+    <t>ZN04.08</t>
+  </si>
+  <si>
+    <t>SOL 109,745,956.56</t>
+  </si>
+  <si>
+    <t>43050000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,746,956.56</t>
+  </si>
+  <si>
+    <t>ZN04.05</t>
+  </si>
+  <si>
+    <t>DEPOS. EN CTA. 0011011301000</t>
+  </si>
+  <si>
+    <t>SOL 109,747,456.56</t>
+  </si>
+  <si>
+    <t>SOL 476.60</t>
+  </si>
+  <si>
+    <t>SOL 109,747,933.16</t>
+  </si>
+  <si>
+    <t>SOL 463.00</t>
+  </si>
+  <si>
+    <t>SOL 109,748,396.16</t>
+  </si>
+  <si>
+    <t>SOL 460.00</t>
+  </si>
+  <si>
+    <t>SOL 109,748,856.16</t>
+  </si>
+  <si>
+    <t>SOL 453.50</t>
+  </si>
+  <si>
+    <t>SOL 109,749,309.66</t>
+  </si>
+  <si>
+    <t>SOL 440.00</t>
+  </si>
+  <si>
+    <t>SOL 109,749,749.66</t>
+  </si>
+  <si>
+    <t>SOL 432.00</t>
+  </si>
+  <si>
+    <t>SOL 109,750,181.66</t>
+  </si>
+  <si>
+    <t>SOL 406.70</t>
+  </si>
+  <si>
+    <t>SOL 109,750,588.36</t>
+  </si>
+  <si>
+    <t>SOL 400.00</t>
+  </si>
+  <si>
+    <t>SOL 109,750,988.36</t>
+  </si>
+  <si>
+    <t>SOL 109,751,388.36</t>
+  </si>
+  <si>
+    <t>82150000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,751,788.36</t>
+  </si>
+  <si>
+    <t>ZN05.01</t>
+  </si>
+  <si>
+    <t>SOL 390.00</t>
+  </si>
+  <si>
+    <t>SOL 109,752,178.36</t>
+  </si>
+  <si>
+    <t>SOL 332.00</t>
+  </si>
+  <si>
+    <t>SOL 109,752,510.36</t>
+  </si>
+  <si>
+    <t>SOL 329.05</t>
+  </si>
+  <si>
+    <t>SOL 109,752,839.41</t>
+  </si>
+  <si>
+    <t>63090000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,753,839.41</t>
+  </si>
+  <si>
+    <t>ZN07.03</t>
+  </si>
+  <si>
+    <t>SOL 326.00</t>
+  </si>
+  <si>
+    <t>SOL 109,754,165.41</t>
+  </si>
+  <si>
+    <t>SOL 325.00</t>
+  </si>
+  <si>
+    <t>SOL 109,754,490.41</t>
+  </si>
+  <si>
+    <t>93230000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,755,490.41</t>
+  </si>
+  <si>
+    <t>ZN03.07</t>
+  </si>
+  <si>
+    <t>SOL 324.00</t>
+  </si>
+  <si>
+    <t>SOL 109,755,814.41</t>
+  </si>
+  <si>
+    <t>SOL 109,756,814.41</t>
+  </si>
+  <si>
+    <t>63020000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 303.00</t>
+  </si>
+  <si>
+    <t>SOL 109,757,117.41</t>
+  </si>
+  <si>
+    <t>ZN07.01</t>
+  </si>
+  <si>
+    <t>72060000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 907.00</t>
+  </si>
+  <si>
+    <t>SOL 109,758,024.41</t>
+  </si>
+  <si>
+    <t>ZN01.03</t>
+  </si>
+  <si>
+    <t>SOL 301.00</t>
+  </si>
+  <si>
+    <t>SOL 109,758,325.41</t>
+  </si>
+  <si>
+    <t>93040000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 903.00</t>
+  </si>
+  <si>
+    <t>SOL 109,759,228.41</t>
+  </si>
+  <si>
+    <t>ZN03.02</t>
+  </si>
+  <si>
+    <t>*33010000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 300.00</t>
+  </si>
+  <si>
+    <t>SOL 109,759,528.41</t>
+  </si>
+  <si>
+    <t>PL02</t>
+  </si>
+  <si>
+    <t>SOL 901.50</t>
+  </si>
+  <si>
+    <t>SOL 109,760,429.91</t>
+  </si>
+  <si>
+    <t>SOL 109,760,729.91</t>
+  </si>
+  <si>
+    <t>93170000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 880.00</t>
+  </si>
+  <si>
+    <t>SOL 109,761,609.91</t>
+  </si>
+  <si>
+    <t>ZN03.12</t>
+  </si>
+  <si>
+    <t>43040000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 292.09</t>
+  </si>
+  <si>
+    <t>SOL 109,761,902.00</t>
+  </si>
+  <si>
+    <t>ZN04.04</t>
+  </si>
+  <si>
+    <t>SOL 289.00</t>
+  </si>
+  <si>
+    <t>SOL 109,762,191.00</t>
+  </si>
+  <si>
+    <t>*43020000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 870.00</t>
+  </si>
+  <si>
+    <t>SOL 109,763,061.00</t>
+  </si>
+  <si>
+    <t>ZN04.02</t>
+  </si>
+  <si>
+    <t>SOL 854.00</t>
+  </si>
+  <si>
+    <t>SOL 109,763,915.00</t>
+  </si>
+  <si>
+    <t>SOL 287.50</t>
+  </si>
+  <si>
+    <t>SOL 109,764,202.50</t>
+  </si>
+  <si>
+    <t>93100000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 850.00</t>
+  </si>
+  <si>
+    <t>SOL 109,765,052.50</t>
+  </si>
+  <si>
+    <t>ZN03.08</t>
+  </si>
+  <si>
+    <t>SOL 284.00</t>
+  </si>
+  <si>
+    <t>SOL 109,765,336.50</t>
+  </si>
+  <si>
+    <t>SOL 800.00</t>
+  </si>
+  <si>
+    <t>SOL 109,766,136.50</t>
+  </si>
+  <si>
+    <t>SOL 277.00</t>
+  </si>
+  <si>
+    <t>SOL 109,766,413.50</t>
+  </si>
+  <si>
+    <t>SOL 275.00</t>
+  </si>
+  <si>
+    <t>SOL 109,766,688.50</t>
+  </si>
+  <si>
+    <t>SOL 799.30</t>
+  </si>
+  <si>
+    <t>SOL 109,767,487.80</t>
+  </si>
+  <si>
+    <t>SOL 273.50</t>
+  </si>
+  <si>
+    <t>SOL 109,767,761.30</t>
+  </si>
+  <si>
+    <t>43110000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 787.00</t>
+  </si>
+  <si>
+    <t>SOL 109,768,548.30</t>
+  </si>
+  <si>
+    <t>ZN04.06</t>
+  </si>
+  <si>
+    <t>SOL 273.20</t>
+  </si>
+  <si>
+    <t>SOL 109,768,821.50</t>
+  </si>
+  <si>
+    <t>SOL 722.30</t>
+  </si>
+  <si>
+    <t>SOL 109,769,543.80</t>
+  </si>
+  <si>
+    <t>JUAN LIZARDO PAREDES MANRIQU</t>
+  </si>
+  <si>
+    <t>SOL 261.50</t>
+  </si>
+  <si>
+    <t>SOL 109,769,805.30</t>
+  </si>
+  <si>
+    <t>10294795117ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 702.80</t>
+  </si>
+  <si>
+    <t>SOL 109,770,508.10</t>
+  </si>
+  <si>
+    <t>C10294795117</t>
+  </si>
+  <si>
+    <t>93200000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 260.00</t>
+  </si>
+  <si>
+    <t>SOL 109,770,768.10</t>
+  </si>
+  <si>
+    <t>ZN03.13</t>
+  </si>
+  <si>
+    <t>SOL 700.00</t>
+  </si>
+  <si>
+    <t>SOL 109,771,468.10</t>
+  </si>
+  <si>
+    <t>10239598884ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,772,168.10</t>
+  </si>
+  <si>
+    <t>C10239598884</t>
+  </si>
+  <si>
+    <t>SOL 256.10</t>
+  </si>
+  <si>
+    <t>SOL 109,772,424.20</t>
+  </si>
+  <si>
+    <t>SOL 256.00</t>
+  </si>
+  <si>
+    <t>SOL 109,772,680.20</t>
+  </si>
+  <si>
+    <t>SOL 680.00</t>
+  </si>
+  <si>
+    <t>SOL 109,773,360.20</t>
+  </si>
+  <si>
+    <t>SOL 255.50</t>
+  </si>
+  <si>
+    <t>SOL 109,773,615.70</t>
+  </si>
+  <si>
+    <t>SOL 674.90</t>
+  </si>
+  <si>
+    <t>SOL 109,774,290.60</t>
+  </si>
+  <si>
+    <t>SOL 250.00</t>
+  </si>
+  <si>
+    <t>SOL 109,774,540.60</t>
+  </si>
+  <si>
+    <t>SOL 665.90</t>
+  </si>
+  <si>
+    <t>SOL 109,775,206.50</t>
+  </si>
+  <si>
+    <t>SOL 650.00</t>
+  </si>
+  <si>
+    <t>SOL 109,775,856.50</t>
+  </si>
+  <si>
+    <t>93130000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 109,776,106.50</t>
+  </si>
+  <si>
+    <t>ZN03.09</t>
+  </si>
+  <si>
+    <t>SOL 642.00</t>
+  </si>
+  <si>
+    <t>SOL 109,776,748.50</t>
+  </si>
+  <si>
+    <t>SOL 627.00</t>
+  </si>
+  <si>
+    <t>SOL 109,777,375.50</t>
+  </si>
+  <si>
+    <t>SOL 618.00</t>
+  </si>
+  <si>
+    <t>SOL 109,777,993.50</t>
+  </si>
+  <si>
+    <t>R20612155977SERVICIOS DE CRI</t>
+  </si>
+  <si>
+    <t>SOL 601.80</t>
+  </si>
+  <si>
+    <t>SOL 109,778,595.30</t>
+  </si>
+  <si>
+    <t>SOL 600.00</t>
+  </si>
+  <si>
+    <t>SOL 109,779,195.30</t>
+  </si>
+  <si>
+    <t>SOL 109,779,795.30</t>
+  </si>
+  <si>
+    <t>SOL 109,780,395.30</t>
+  </si>
+  <si>
+    <t>SOL 594.00</t>
+  </si>
+  <si>
+    <t>SOL 109,780,989.30</t>
+  </si>
+  <si>
+    <t>*93150000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 573.00</t>
+  </si>
+  <si>
+    <t>SOL 109,781,562.30</t>
+  </si>
+  <si>
+    <t>SOL 109,781,812.30</t>
+  </si>
+  <si>
+    <t>SOL 570.00</t>
+  </si>
+  <si>
+    <t>SOL 109,782,382.30</t>
+  </si>
+  <si>
+    <t>SOL 550.00</t>
+  </si>
+  <si>
+    <t>SOL 109,782,932.30</t>
+  </si>
+  <si>
+    <t>SOL 540.00</t>
+  </si>
+  <si>
+    <t>SOL 109,783,472.30</t>
+  </si>
+  <si>
+    <t>SOL 530.00</t>
+  </si>
+  <si>
+    <t>SOL 109,784,002.30</t>
+  </si>
+  <si>
+    <t>SOL 109,784,502.30</t>
+  </si>
+  <si>
+    <t>SOL 246.08</t>
+  </si>
+  <si>
+    <t>SOL 109,784,748.38</t>
+  </si>
+  <si>
+    <t>SOL 240.00</t>
+  </si>
+  <si>
+    <t>SOL 109,784,988.38</t>
+  </si>
+  <si>
+    <t>SOL 212.00</t>
+  </si>
+  <si>
+    <t>SOL 109,785,200.38</t>
+  </si>
+  <si>
+    <t>*43010000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 210.50</t>
+  </si>
+  <si>
+    <t>SOL 109,785,410.88</t>
+  </si>
+  <si>
+    <t>SOL 210.00</t>
+  </si>
+  <si>
+    <t>SOL 109,785,620.88</t>
+  </si>
+  <si>
+    <t>SOL 201.50</t>
+  </si>
+  <si>
+    <t>SOL 109,785,822.38</t>
+  </si>
+  <si>
+    <t>SOL 200.00</t>
+  </si>
+  <si>
+    <t>SOL 109,786,022.38</t>
+  </si>
+  <si>
+    <t>SOL 109,786,222.38</t>
+  </si>
+  <si>
+    <t>SOL 197.00</t>
+  </si>
+  <si>
+    <t>SOL 109,786,419.38</t>
+  </si>
+  <si>
+    <t>SOL 109,786,616.38</t>
+  </si>
+  <si>
+    <t>SOL 190.00</t>
+  </si>
+  <si>
+    <t>SOL 109,786,806.38</t>
+  </si>
+  <si>
+    <t>SOL 181.50</t>
+  </si>
+  <si>
+    <t>SOL 109,786,987.88</t>
+  </si>
+  <si>
+    <t>SOL 179.80</t>
+  </si>
+  <si>
+    <t>SOL 109,787,167.68</t>
+  </si>
+  <si>
+    <t>SOL 176.00</t>
+  </si>
+  <si>
+    <t>SOL 109,787,343.68</t>
+  </si>
+  <si>
+    <t>SOL 150.00</t>
+  </si>
+  <si>
+    <t>SOL 109,787,493.68</t>
+  </si>
+  <si>
+    <t>SOL 141.70</t>
+  </si>
+  <si>
+    <t>SOL 109,787,635.38</t>
+  </si>
+  <si>
+    <t>SOL 134.00</t>
+  </si>
+  <si>
+    <t>SOL 109,787,769.38</t>
+  </si>
+  <si>
+    <t>SOL 133.48</t>
+  </si>
+  <si>
+    <t>SOL 109,787,902.86</t>
+  </si>
+  <si>
+    <t>SOL 130.90</t>
+  </si>
+  <si>
+    <t>SOL 109,788,033.76</t>
+  </si>
+  <si>
+    <t>R20100366747LLAMA GAS SA</t>
+  </si>
+  <si>
+    <t>SOL 126.00</t>
+  </si>
+  <si>
+    <t>SOL 109,788,159.76</t>
+  </si>
+  <si>
+    <t>SOL 108.00</t>
+  </si>
+  <si>
+    <t>SOL 109,788,267.76</t>
+  </si>
+  <si>
+    <t>SOL 106.80</t>
+  </si>
+  <si>
+    <t>SOL 109,788,374.56</t>
+  </si>
+  <si>
+    <t>SOL 106.00</t>
+  </si>
+  <si>
+    <t>SOL 109,788,480.56</t>
+  </si>
+  <si>
+    <t>SOL 101.00</t>
+  </si>
+  <si>
+    <t>SOL 109,788,581.56</t>
+  </si>
+  <si>
+    <t>SOL 100.00</t>
+  </si>
+  <si>
+    <t>SOL 109,788,681.56</t>
+  </si>
+  <si>
+    <t>SOL 68.00</t>
+  </si>
+  <si>
+    <t>SOL 109,788,749.56</t>
+  </si>
+  <si>
+    <t>*82150000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 64.50</t>
+  </si>
+  <si>
+    <t>SOL 109,788,814.06</t>
+  </si>
+  <si>
+    <t>PIERA LARISSA QUIÑONES SPADA</t>
+  </si>
+  <si>
+    <t>SOL 64.00</t>
+  </si>
+  <si>
+    <t>SOL 109,788,878.06</t>
+  </si>
+  <si>
+    <t>SOL 63.00</t>
+  </si>
+  <si>
+    <t>SOL 109,788,941.06</t>
+  </si>
+  <si>
+    <t>*63010000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 61.90</t>
+  </si>
+  <si>
+    <t>SOL 109,789,002.96</t>
+  </si>
+  <si>
+    <t>PL07</t>
+  </si>
+  <si>
+    <t>SOL 61.00</t>
+  </si>
+  <si>
+    <t>SOL 109,789,063.96</t>
+  </si>
+  <si>
+    <t>COMISION REC</t>
+  </si>
+  <si>
+    <t>SOL 2.50</t>
+  </si>
+  <si>
+    <t>SOL 109,789,061.46</t>
+  </si>
+  <si>
+    <t>*20202020 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 55.00</t>
+  </si>
+  <si>
+    <t>SOL 109,789,116.46</t>
+  </si>
+  <si>
+    <t>SOL 53.00</t>
+  </si>
+  <si>
+    <t>SOL 109,789,169.46</t>
+  </si>
+  <si>
+    <t>SOL 109,789,222.46</t>
+  </si>
+  <si>
+    <t>SOL 51.00</t>
+  </si>
+  <si>
+    <t>SOL 109,789,273.46</t>
+  </si>
+  <si>
+    <t>SOL 50.50</t>
+  </si>
+  <si>
+    <t>SOL 109,789,323.96</t>
+  </si>
+  <si>
+    <t>*COMISION REC</t>
+  </si>
+  <si>
+    <t>SOL 1.50</t>
+  </si>
+  <si>
+    <t>SOL 109,789,322.46</t>
+  </si>
+  <si>
+    <t>SOL 50.00</t>
+  </si>
+  <si>
+    <t>SOL 109,789,372.46</t>
+  </si>
+  <si>
+    <t>SOL 109,789,422.46</t>
+  </si>
+  <si>
+    <t>SOL 40.90</t>
+  </si>
+  <si>
+    <t>SOL 109,789,463.36</t>
+  </si>
+  <si>
+    <t>SOL 39.00</t>
+  </si>
+  <si>
+    <t>SOL 109,789,502.36</t>
+  </si>
+  <si>
+    <t>SOL 32.21</t>
+  </si>
+  <si>
+    <t>SOL 109,789,534.57</t>
+  </si>
+  <si>
+    <t>SOL 27.90</t>
+  </si>
+  <si>
+    <t>SOL 109,789,562.47</t>
+  </si>
+  <si>
+    <t>*33030000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 19.40</t>
+  </si>
+  <si>
+    <t>SOL 109,789,581.87</t>
+  </si>
+  <si>
+    <t>SOL 15.00</t>
+  </si>
+  <si>
+    <t>SOL 109,789,596.87</t>
+  </si>
+  <si>
+    <t>SOL 11.00</t>
+  </si>
+  <si>
+    <t>SOL 109,789,607.87</t>
+  </si>
+  <si>
+    <t>*72100000 ABONO VARIOS</t>
+  </si>
+  <si>
+    <t>SOL 10.00</t>
+  </si>
+  <si>
+    <t>SOL 109,789,617.87</t>
+  </si>
+  <si>
+    <t>ZN01.07</t>
+  </si>
+  <si>
+    <t>SOL 9.00</t>
+  </si>
+  <si>
+    <t>SOL 109,789,626.87</t>
+  </si>
+  <si>
+    <t>SOL 6.70</t>
+  </si>
+  <si>
+    <t>SOL 109,789,633.57</t>
+  </si>
+  <si>
+    <t>SOL 4.00</t>
+  </si>
+  <si>
+    <t>SOL 109,789,629.57</t>
+  </si>
+  <si>
+    <t>ITF</t>
+  </si>
+  <si>
+    <t>SOL 0.05</t>
+  </si>
+  <si>
+    <t>SOL 109,789,629.52</t>
+  </si>
+  <si>
+    <t>C20520182692</t>
+  </si>
+  <si>
+    <t>SOL 6.65</t>
+  </si>
+  <si>
+    <t>SOL 109,789,622.87</t>
+  </si>
+  <si>
+    <t>COMISION TRANSFERENCIAS</t>
+  </si>
+  <si>
+    <t>SOL 22.00</t>
+  </si>
+  <si>
+    <t>SOL 109,789,600.87</t>
+  </si>
+  <si>
+    <t>*C/ PROVEEDO.0318003</t>
+  </si>
+  <si>
+    <t>SOL 109,789,474.87</t>
+  </si>
+  <si>
+    <t>SOL 2.00</t>
+  </si>
+  <si>
+    <t>SOL 109,789,472.87</t>
+  </si>
+  <si>
+    <t>*C/ PROVEEDO.0318005</t>
+  </si>
+  <si>
+    <t>SOL 5,575.20</t>
+  </si>
+  <si>
+    <t>SOL 109,783,897.67</t>
+  </si>
+  <si>
+    <t>SOL 2.30</t>
+  </si>
+  <si>
+    <t>SOL 109,783,895.37</t>
+  </si>
+  <si>
+    <t>*C/ PROVEEDO.0318002</t>
+  </si>
+  <si>
+    <t>SOL 133,272.47</t>
+  </si>
+  <si>
+    <t>SOL 109,650,622.90</t>
+  </si>
+  <si>
+    <t>CCI INTERBANK LLAMAGAS</t>
+  </si>
+  <si>
+    <t>SOL 600,000.00</t>
+  </si>
+  <si>
+    <t>SOL 109,050,622.90</t>
+  </si>
+  <si>
+    <t>SOL 0.10</t>
+  </si>
+  <si>
+    <t>SOL 109,050,622.80</t>
+  </si>
+  <si>
+    <t>SOL 0.15</t>
+  </si>
+  <si>
+    <t>SOL 109,050,622.65</t>
+  </si>
+  <si>
+    <t>SOL 0.20</t>
+  </si>
+  <si>
+    <t>SOL 109,050,622.45</t>
+  </si>
+  <si>
+    <t>SOL 0.25</t>
+  </si>
+  <si>
+    <t>SOL 109,050,622.20</t>
+  </si>
+  <si>
+    <t>SOL 0.30</t>
+  </si>
+  <si>
+    <t>SOL 109,050,621.90</t>
+  </si>
+  <si>
+    <t>SOL 0.35</t>
+  </si>
+  <si>
+    <t>SOL 109,050,621.55</t>
+  </si>
+  <si>
+    <t>SOL 0.50</t>
+  </si>
+  <si>
+    <t>SOL 109,050,621.05</t>
+  </si>
+  <si>
+    <t>SOL 0.55</t>
+  </si>
+  <si>
+    <t>SOL 109,050,620.50</t>
+  </si>
+  <si>
+    <t>SOL 0.60</t>
+  </si>
+  <si>
+    <t>SOL 109,050,619.90</t>
+  </si>
+  <si>
+    <t>SOL 1.10</t>
+  </si>
+  <si>
+    <t>SOL 109,050,618.80</t>
+  </si>
+  <si>
+    <t>x|</t>
   </si>
 </sst>
 </file>
@@ -211,7 +1649,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -222,6 +1660,7 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -237,10 +1676,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -630,6 +2065,4950 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E096031-DAE3-4165-96DD-23087106CC63}">
+  <dimension ref="A1:O190"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="D2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="B3" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C3">
+        <v>1922952</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="B4" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C4" t="s">
+        <v>509</v>
+      </c>
+      <c r="D4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="B5" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C5">
+        <v>1923108</v>
+      </c>
+      <c r="D5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="B6" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C6">
+        <v>1923058</v>
+      </c>
+      <c r="D6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="B7" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C7">
+        <v>1922711</v>
+      </c>
+      <c r="D7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="B8" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C8">
+        <v>1922947</v>
+      </c>
+      <c r="D8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="B9" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C9">
+        <v>1922762</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" t="s">
+        <v>47</v>
+      </c>
+      <c r="L9" t="s">
+        <v>72</v>
+      </c>
+      <c r="O9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="B10" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C10">
+        <v>1923130</v>
+      </c>
+      <c r="D10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" t="s">
+        <v>47</v>
+      </c>
+      <c r="L10" t="s">
+        <v>75</v>
+      </c>
+      <c r="O10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="B11" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C11">
+        <v>1922858</v>
+      </c>
+      <c r="D11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L11" t="s">
+        <v>79</v>
+      </c>
+      <c r="O11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="B12" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C12">
+        <v>1923167</v>
+      </c>
+      <c r="D12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12" t="s">
+        <v>81</v>
+      </c>
+      <c r="I12" t="s">
+        <v>47</v>
+      </c>
+      <c r="L12" t="s">
+        <v>82</v>
+      </c>
+      <c r="O12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="B13" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C13">
+        <v>1922893</v>
+      </c>
+      <c r="D13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" t="s">
+        <v>47</v>
+      </c>
+      <c r="L13" t="s">
+        <v>86</v>
+      </c>
+      <c r="O13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="B14" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C14">
+        <v>1923074</v>
+      </c>
+      <c r="D14" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14" t="s">
+        <v>47</v>
+      </c>
+      <c r="L14" t="s">
+        <v>89</v>
+      </c>
+      <c r="O14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="B15" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C15">
+        <v>1922914</v>
+      </c>
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" t="s">
+        <v>47</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="B16" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C16">
+        <v>1922944</v>
+      </c>
+      <c r="D16" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H16" t="s">
+        <v>95</v>
+      </c>
+      <c r="I16" t="s">
+        <v>47</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="O16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15">
+      <c r="B17" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C17">
+        <v>1922739</v>
+      </c>
+      <c r="D17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" t="s">
+        <v>97</v>
+      </c>
+      <c r="I17" t="s">
+        <v>47</v>
+      </c>
+      <c r="L17" t="s">
+        <v>75</v>
+      </c>
+      <c r="O17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15">
+      <c r="B18" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C18">
+        <v>1922899</v>
+      </c>
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" t="s">
+        <v>100</v>
+      </c>
+      <c r="I18" t="s">
+        <v>47</v>
+      </c>
+      <c r="L18" t="s">
+        <v>101</v>
+      </c>
+      <c r="O18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15">
+      <c r="B19" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C19">
+        <v>1922864</v>
+      </c>
+      <c r="D19" t="s">
+        <v>102</v>
+      </c>
+      <c r="G19" t="s">
+        <v>103</v>
+      </c>
+      <c r="H19" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" t="s">
+        <v>47</v>
+      </c>
+      <c r="L19" t="s">
+        <v>105</v>
+      </c>
+      <c r="O19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15">
+      <c r="B20" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C20">
+        <v>1923092</v>
+      </c>
+      <c r="D20" t="s">
+        <v>106</v>
+      </c>
+      <c r="G20" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" t="s">
+        <v>47</v>
+      </c>
+      <c r="L20" t="s">
+        <v>109</v>
+      </c>
+      <c r="O20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15">
+      <c r="B21" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C21">
+        <v>1922998</v>
+      </c>
+      <c r="D21" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21" t="s">
+        <v>57</v>
+      </c>
+      <c r="H21" t="s">
+        <v>111</v>
+      </c>
+      <c r="I21" t="s">
+        <v>47</v>
+      </c>
+      <c r="L21" t="s">
+        <v>112</v>
+      </c>
+      <c r="O21" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15">
+      <c r="B22" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C22">
+        <v>1923029</v>
+      </c>
+      <c r="D22" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22" t="s">
+        <v>107</v>
+      </c>
+      <c r="H22" t="s">
+        <v>114</v>
+      </c>
+      <c r="I22" t="s">
+        <v>47</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15">
+      <c r="B23" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C23">
+        <v>1922887</v>
+      </c>
+      <c r="D23" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" t="s">
+        <v>115</v>
+      </c>
+      <c r="H23" t="s">
+        <v>116</v>
+      </c>
+      <c r="I23" t="s">
+        <v>47</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="O23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15">
+      <c r="B24" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C24">
+        <v>1922697</v>
+      </c>
+      <c r="D24" t="s">
+        <v>117</v>
+      </c>
+      <c r="G24" t="s">
+        <v>57</v>
+      </c>
+      <c r="H24" t="s">
+        <v>118</v>
+      </c>
+      <c r="I24" t="s">
+        <v>47</v>
+      </c>
+      <c r="L24" t="s">
+        <v>86</v>
+      </c>
+      <c r="O24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15">
+      <c r="B25" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C25">
+        <v>1922715</v>
+      </c>
+      <c r="D25" t="s">
+        <v>119</v>
+      </c>
+      <c r="G25" t="s">
+        <v>120</v>
+      </c>
+      <c r="H25" t="s">
+        <v>121</v>
+      </c>
+      <c r="I25" t="s">
+        <v>47</v>
+      </c>
+      <c r="L25" t="s">
+        <v>122</v>
+      </c>
+      <c r="O25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15">
+      <c r="B26" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C26">
+        <v>1922940</v>
+      </c>
+      <c r="D26" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26" t="s">
+        <v>57</v>
+      </c>
+      <c r="H26" t="s">
+        <v>124</v>
+      </c>
+      <c r="I26" t="s">
+        <v>47</v>
+      </c>
+      <c r="L26" t="s">
+        <v>125</v>
+      </c>
+      <c r="O26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15">
+      <c r="B27" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C27">
+        <v>1922782</v>
+      </c>
+      <c r="D27" t="s">
+        <v>126</v>
+      </c>
+      <c r="G27" t="s">
+        <v>127</v>
+      </c>
+      <c r="H27" t="s">
+        <v>128</v>
+      </c>
+      <c r="I27" t="s">
+        <v>47</v>
+      </c>
+      <c r="L27" t="s">
+        <v>129</v>
+      </c>
+      <c r="O27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15">
+      <c r="B28" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C28">
+        <v>1922734</v>
+      </c>
+      <c r="D28" t="s">
+        <v>130</v>
+      </c>
+      <c r="G28" t="s">
+        <v>131</v>
+      </c>
+      <c r="H28" t="s">
+        <v>132</v>
+      </c>
+      <c r="I28" t="s">
+        <v>47</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="O28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15">
+      <c r="B29" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C29">
+        <v>1923159</v>
+      </c>
+      <c r="D29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G29" t="s">
+        <v>57</v>
+      </c>
+      <c r="H29" t="s">
+        <v>134</v>
+      </c>
+      <c r="I29" t="s">
+        <v>47</v>
+      </c>
+      <c r="L29" t="s">
+        <v>135</v>
+      </c>
+      <c r="O29" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15">
+      <c r="B30" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C30">
+        <v>1922902</v>
+      </c>
+      <c r="D30" t="s">
+        <v>136</v>
+      </c>
+      <c r="G30" t="s">
+        <v>137</v>
+      </c>
+      <c r="H30" t="s">
+        <v>138</v>
+      </c>
+      <c r="I30" t="s">
+        <v>47</v>
+      </c>
+      <c r="L30" t="s">
+        <v>139</v>
+      </c>
+      <c r="O30" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15">
+      <c r="B31" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C31">
+        <v>1922768</v>
+      </c>
+      <c r="D31" t="s">
+        <v>140</v>
+      </c>
+      <c r="G31" t="s">
+        <v>57</v>
+      </c>
+      <c r="H31" t="s">
+        <v>141</v>
+      </c>
+      <c r="I31" t="s">
+        <v>47</v>
+      </c>
+      <c r="L31" t="s">
+        <v>142</v>
+      </c>
+      <c r="O31" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15">
+      <c r="B32" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C32">
+        <v>1922838</v>
+      </c>
+      <c r="D32" t="s">
+        <v>143</v>
+      </c>
+      <c r="G32" t="s">
+        <v>144</v>
+      </c>
+      <c r="H32" t="s">
+        <v>145</v>
+      </c>
+      <c r="I32" t="s">
+        <v>47</v>
+      </c>
+      <c r="L32" t="s">
+        <v>146</v>
+      </c>
+      <c r="O32" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15">
+      <c r="B33" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C33">
+        <v>1922794</v>
+      </c>
+      <c r="D33" t="s">
+        <v>147</v>
+      </c>
+      <c r="G33" t="s">
+        <v>148</v>
+      </c>
+      <c r="H33" t="s">
+        <v>149</v>
+      </c>
+      <c r="I33" t="s">
+        <v>47</v>
+      </c>
+      <c r="L33" t="s">
+        <v>150</v>
+      </c>
+      <c r="O33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15">
+      <c r="B34" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C34">
+        <v>1922852</v>
+      </c>
+      <c r="D34" t="s">
+        <v>151</v>
+      </c>
+      <c r="G34" t="s">
+        <v>152</v>
+      </c>
+      <c r="H34" t="s">
+        <v>153</v>
+      </c>
+      <c r="I34" t="s">
+        <v>47</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="O34" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15">
+      <c r="B35" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C35">
+        <v>1922830</v>
+      </c>
+      <c r="D35" t="s">
+        <v>154</v>
+      </c>
+      <c r="G35" t="s">
+        <v>155</v>
+      </c>
+      <c r="H35" t="s">
+        <v>156</v>
+      </c>
+      <c r="I35" t="s">
+        <v>47</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="O35" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15">
+      <c r="B36" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C36">
+        <v>1922801</v>
+      </c>
+      <c r="D36" t="s">
+        <v>157</v>
+      </c>
+      <c r="G36" t="s">
+        <v>57</v>
+      </c>
+      <c r="H36" t="s">
+        <v>158</v>
+      </c>
+      <c r="I36" t="s">
+        <v>47</v>
+      </c>
+      <c r="L36" t="s">
+        <v>159</v>
+      </c>
+      <c r="O36" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15">
+      <c r="B37" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C37">
+        <v>1922879</v>
+      </c>
+      <c r="D37" t="s">
+        <v>66</v>
+      </c>
+      <c r="G37" t="s">
+        <v>160</v>
+      </c>
+      <c r="H37" t="s">
+        <v>161</v>
+      </c>
+      <c r="I37" t="s">
+        <v>47</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="O37" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15">
+      <c r="B38" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C38">
+        <v>1922785</v>
+      </c>
+      <c r="D38" t="s">
+        <v>162</v>
+      </c>
+      <c r="G38" t="s">
+        <v>163</v>
+      </c>
+      <c r="H38" t="s">
+        <v>164</v>
+      </c>
+      <c r="I38" t="s">
+        <v>47</v>
+      </c>
+      <c r="L38" t="s">
+        <v>165</v>
+      </c>
+      <c r="O38" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15">
+      <c r="B39" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C39">
+        <v>1922975</v>
+      </c>
+      <c r="D39" t="s">
+        <v>166</v>
+      </c>
+      <c r="G39" t="s">
+        <v>167</v>
+      </c>
+      <c r="H39" t="s">
+        <v>168</v>
+      </c>
+      <c r="I39" t="s">
+        <v>47</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="O39" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15">
+      <c r="B40" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C40">
+        <v>1922799</v>
+      </c>
+      <c r="D40" t="s">
+        <v>169</v>
+      </c>
+      <c r="G40" t="s">
+        <v>57</v>
+      </c>
+      <c r="H40" t="s">
+        <v>170</v>
+      </c>
+      <c r="I40" t="s">
+        <v>47</v>
+      </c>
+      <c r="L40" t="s">
+        <v>171</v>
+      </c>
+      <c r="O40" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15">
+      <c r="B41" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C41">
+        <v>1922803</v>
+      </c>
+      <c r="D41" t="s">
+        <v>147</v>
+      </c>
+      <c r="G41" t="s">
+        <v>172</v>
+      </c>
+      <c r="H41" t="s">
+        <v>173</v>
+      </c>
+      <c r="I41" t="s">
+        <v>47</v>
+      </c>
+      <c r="L41" t="s">
+        <v>150</v>
+      </c>
+      <c r="O41" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15">
+      <c r="B42" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C42">
+        <v>1923024</v>
+      </c>
+      <c r="D42" t="s">
+        <v>83</v>
+      </c>
+      <c r="G42" t="s">
+        <v>174</v>
+      </c>
+      <c r="H42" t="s">
+        <v>175</v>
+      </c>
+      <c r="I42" t="s">
+        <v>47</v>
+      </c>
+      <c r="L42" t="s">
+        <v>86</v>
+      </c>
+      <c r="O42" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15">
+      <c r="B43" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C43">
+        <v>1922790</v>
+      </c>
+      <c r="D43" t="s">
+        <v>176</v>
+      </c>
+      <c r="G43" t="s">
+        <v>57</v>
+      </c>
+      <c r="H43" t="s">
+        <v>177</v>
+      </c>
+      <c r="I43" t="s">
+        <v>47</v>
+      </c>
+      <c r="L43" t="s">
+        <v>178</v>
+      </c>
+      <c r="O43" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15">
+      <c r="B44" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C44">
+        <v>1922949</v>
+      </c>
+      <c r="D44" t="s">
+        <v>147</v>
+      </c>
+      <c r="G44" t="s">
+        <v>179</v>
+      </c>
+      <c r="H44" t="s">
+        <v>180</v>
+      </c>
+      <c r="I44" t="s">
+        <v>47</v>
+      </c>
+      <c r="L44" t="s">
+        <v>150</v>
+      </c>
+      <c r="O44" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15">
+      <c r="B45" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C45">
+        <v>1922822</v>
+      </c>
+      <c r="D45" t="s">
+        <v>181</v>
+      </c>
+      <c r="G45" t="s">
+        <v>57</v>
+      </c>
+      <c r="H45" t="s">
+        <v>182</v>
+      </c>
+      <c r="I45" t="s">
+        <v>47</v>
+      </c>
+      <c r="L45" t="s">
+        <v>183</v>
+      </c>
+      <c r="O45" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15">
+      <c r="B46" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C46">
+        <v>1923097</v>
+      </c>
+      <c r="D46" t="s">
+        <v>106</v>
+      </c>
+      <c r="G46" t="s">
+        <v>179</v>
+      </c>
+      <c r="H46" t="s">
+        <v>184</v>
+      </c>
+      <c r="I46" t="s">
+        <v>47</v>
+      </c>
+      <c r="L46" t="s">
+        <v>109</v>
+      </c>
+      <c r="O46" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15">
+      <c r="B47" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C47">
+        <v>1923136</v>
+      </c>
+      <c r="D47" t="s">
+        <v>185</v>
+      </c>
+      <c r="G47" t="s">
+        <v>179</v>
+      </c>
+      <c r="H47" t="s">
+        <v>186</v>
+      </c>
+      <c r="I47" t="s">
+        <v>47</v>
+      </c>
+      <c r="L47" t="s">
+        <v>187</v>
+      </c>
+      <c r="O47" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15">
+      <c r="B48" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C48">
+        <v>1922729</v>
+      </c>
+      <c r="D48" t="s">
+        <v>188</v>
+      </c>
+      <c r="G48" t="s">
+        <v>57</v>
+      </c>
+      <c r="H48" t="s">
+        <v>189</v>
+      </c>
+      <c r="I48" t="s">
+        <v>47</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="O48" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15">
+      <c r="B49" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C49">
+        <v>1922766</v>
+      </c>
+      <c r="D49" t="s">
+        <v>140</v>
+      </c>
+      <c r="G49" t="s">
+        <v>190</v>
+      </c>
+      <c r="H49" t="s">
+        <v>191</v>
+      </c>
+      <c r="I49" t="s">
+        <v>47</v>
+      </c>
+      <c r="L49" t="s">
+        <v>142</v>
+      </c>
+      <c r="O49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15">
+      <c r="B50" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C50">
+        <v>1922778</v>
+      </c>
+      <c r="D50" t="s">
+        <v>106</v>
+      </c>
+      <c r="G50" t="s">
+        <v>192</v>
+      </c>
+      <c r="H50" t="s">
+        <v>193</v>
+      </c>
+      <c r="I50" t="s">
+        <v>47</v>
+      </c>
+      <c r="L50" t="s">
+        <v>109</v>
+      </c>
+      <c r="O50" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="2:15">
+      <c r="B51" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C51">
+        <v>1923076</v>
+      </c>
+      <c r="D51" t="s">
+        <v>117</v>
+      </c>
+      <c r="G51" t="s">
+        <v>194</v>
+      </c>
+      <c r="H51" t="s">
+        <v>195</v>
+      </c>
+      <c r="I51" t="s">
+        <v>47</v>
+      </c>
+      <c r="L51" t="s">
+        <v>86</v>
+      </c>
+      <c r="O51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="2:15">
+      <c r="B52" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C52">
+        <v>1922928</v>
+      </c>
+      <c r="D52" t="s">
+        <v>136</v>
+      </c>
+      <c r="G52" t="s">
+        <v>196</v>
+      </c>
+      <c r="H52" t="s">
+        <v>197</v>
+      </c>
+      <c r="I52" t="s">
+        <v>47</v>
+      </c>
+      <c r="L52" t="s">
+        <v>139</v>
+      </c>
+      <c r="O52" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15">
+      <c r="B53" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C53">
+        <v>1923007</v>
+      </c>
+      <c r="D53" t="s">
+        <v>110</v>
+      </c>
+      <c r="G53" t="s">
+        <v>198</v>
+      </c>
+      <c r="H53" t="s">
+        <v>199</v>
+      </c>
+      <c r="I53" t="s">
+        <v>47</v>
+      </c>
+      <c r="L53" t="s">
+        <v>112</v>
+      </c>
+      <c r="O53" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15">
+      <c r="B54" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C54">
+        <v>1922718</v>
+      </c>
+      <c r="D54" t="s">
+        <v>140</v>
+      </c>
+      <c r="G54" t="s">
+        <v>200</v>
+      </c>
+      <c r="H54" t="s">
+        <v>201</v>
+      </c>
+      <c r="I54" t="s">
+        <v>47</v>
+      </c>
+      <c r="L54" t="s">
+        <v>142</v>
+      </c>
+      <c r="O54" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="2:15">
+      <c r="B55" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C55">
+        <v>1923054</v>
+      </c>
+      <c r="D55" t="s">
+        <v>87</v>
+      </c>
+      <c r="G55" t="s">
+        <v>202</v>
+      </c>
+      <c r="H55" t="s">
+        <v>203</v>
+      </c>
+      <c r="I55" t="s">
+        <v>47</v>
+      </c>
+      <c r="L55" t="s">
+        <v>89</v>
+      </c>
+      <c r="O55" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15">
+      <c r="B56" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C56">
+        <v>1923134</v>
+      </c>
+      <c r="D56" t="s">
+        <v>73</v>
+      </c>
+      <c r="G56" t="s">
+        <v>204</v>
+      </c>
+      <c r="H56" t="s">
+        <v>205</v>
+      </c>
+      <c r="I56" t="s">
+        <v>47</v>
+      </c>
+      <c r="L56" t="s">
+        <v>75</v>
+      </c>
+      <c r="O56" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="2:15">
+      <c r="B57" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C57">
+        <v>1923042</v>
+      </c>
+      <c r="D57" t="s">
+        <v>87</v>
+      </c>
+      <c r="G57" t="s">
+        <v>204</v>
+      </c>
+      <c r="H57" t="s">
+        <v>206</v>
+      </c>
+      <c r="I57" t="s">
+        <v>47</v>
+      </c>
+      <c r="L57" t="s">
+        <v>89</v>
+      </c>
+      <c r="O57" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="58" spans="2:15">
+      <c r="B58" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C58">
+        <v>1922727</v>
+      </c>
+      <c r="D58" t="s">
+        <v>207</v>
+      </c>
+      <c r="G58" t="s">
+        <v>204</v>
+      </c>
+      <c r="H58" t="s">
+        <v>208</v>
+      </c>
+      <c r="I58" t="s">
+        <v>47</v>
+      </c>
+      <c r="L58" t="s">
+        <v>209</v>
+      </c>
+      <c r="O58" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="59" spans="2:15">
+      <c r="B59" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C59">
+        <v>1922726</v>
+      </c>
+      <c r="D59" t="s">
+        <v>188</v>
+      </c>
+      <c r="G59" t="s">
+        <v>210</v>
+      </c>
+      <c r="H59" t="s">
+        <v>211</v>
+      </c>
+      <c r="I59" t="s">
+        <v>47</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="O59" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="60" spans="2:15">
+      <c r="B60" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C60">
+        <v>1923066</v>
+      </c>
+      <c r="D60" t="s">
+        <v>87</v>
+      </c>
+      <c r="G60" t="s">
+        <v>212</v>
+      </c>
+      <c r="H60" t="s">
+        <v>213</v>
+      </c>
+      <c r="I60" t="s">
+        <v>47</v>
+      </c>
+      <c r="L60" t="s">
+        <v>89</v>
+      </c>
+      <c r="O60" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="61" spans="2:15">
+      <c r="B61" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C61">
+        <v>1922965</v>
+      </c>
+      <c r="D61" t="s">
+        <v>123</v>
+      </c>
+      <c r="G61" t="s">
+        <v>214</v>
+      </c>
+      <c r="H61" t="s">
+        <v>215</v>
+      </c>
+      <c r="I61" t="s">
+        <v>47</v>
+      </c>
+      <c r="L61" t="s">
+        <v>125</v>
+      </c>
+      <c r="O61" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="62" spans="2:15">
+      <c r="B62" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C62">
+        <v>1922956</v>
+      </c>
+      <c r="D62" t="s">
+        <v>216</v>
+      </c>
+      <c r="G62" t="s">
+        <v>179</v>
+      </c>
+      <c r="H62" t="s">
+        <v>217</v>
+      </c>
+      <c r="I62" t="s">
+        <v>47</v>
+      </c>
+      <c r="L62" t="s">
+        <v>218</v>
+      </c>
+      <c r="O62" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="63" spans="2:15">
+      <c r="B63" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C63">
+        <v>1923116</v>
+      </c>
+      <c r="D63" t="s">
+        <v>185</v>
+      </c>
+      <c r="G63" t="s">
+        <v>219</v>
+      </c>
+      <c r="H63" t="s">
+        <v>220</v>
+      </c>
+      <c r="I63" t="s">
+        <v>47</v>
+      </c>
+      <c r="L63" t="s">
+        <v>187</v>
+      </c>
+      <c r="O63" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="64" spans="2:15">
+      <c r="B64" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C64">
+        <v>1923161</v>
+      </c>
+      <c r="D64" t="s">
+        <v>133</v>
+      </c>
+      <c r="G64" t="s">
+        <v>221</v>
+      </c>
+      <c r="H64" t="s">
+        <v>222</v>
+      </c>
+      <c r="I64" t="s">
+        <v>47</v>
+      </c>
+      <c r="L64" t="s">
+        <v>135</v>
+      </c>
+      <c r="O64" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15">
+      <c r="B65" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C65">
+        <v>1922845</v>
+      </c>
+      <c r="D65" t="s">
+        <v>223</v>
+      </c>
+      <c r="G65" t="s">
+        <v>179</v>
+      </c>
+      <c r="H65" t="s">
+        <v>224</v>
+      </c>
+      <c r="I65" t="s">
+        <v>47</v>
+      </c>
+      <c r="L65" t="s">
+        <v>225</v>
+      </c>
+      <c r="O65" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15">
+      <c r="B66" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C66">
+        <v>1923163</v>
+      </c>
+      <c r="D66" t="s">
+        <v>143</v>
+      </c>
+      <c r="G66" t="s">
+        <v>226</v>
+      </c>
+      <c r="H66" t="s">
+        <v>227</v>
+      </c>
+      <c r="I66" t="s">
+        <v>47</v>
+      </c>
+      <c r="L66" t="s">
+        <v>146</v>
+      </c>
+      <c r="O66" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15">
+      <c r="B67" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C67">
+        <v>1922742</v>
+      </c>
+      <c r="D67" t="s">
+        <v>140</v>
+      </c>
+      <c r="G67" t="s">
+        <v>179</v>
+      </c>
+      <c r="H67" t="s">
+        <v>228</v>
+      </c>
+      <c r="I67" t="s">
+        <v>47</v>
+      </c>
+      <c r="L67" t="s">
+        <v>142</v>
+      </c>
+      <c r="O67" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="68" spans="2:15">
+      <c r="B68" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C68">
+        <v>1923120</v>
+      </c>
+      <c r="D68" t="s">
+        <v>229</v>
+      </c>
+      <c r="G68" t="s">
+        <v>230</v>
+      </c>
+      <c r="H68" t="s">
+        <v>231</v>
+      </c>
+      <c r="I68" t="s">
+        <v>47</v>
+      </c>
+      <c r="L68" t="s">
+        <v>232</v>
+      </c>
+      <c r="O68" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15">
+      <c r="B69" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C69">
+        <v>1923124</v>
+      </c>
+      <c r="D69" t="s">
+        <v>233</v>
+      </c>
+      <c r="G69" t="s">
+        <v>234</v>
+      </c>
+      <c r="H69" t="s">
+        <v>235</v>
+      </c>
+      <c r="I69" t="s">
+        <v>47</v>
+      </c>
+      <c r="L69" t="s">
+        <v>236</v>
+      </c>
+      <c r="O69" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15">
+      <c r="B70" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C70">
+        <v>1923182</v>
+      </c>
+      <c r="D70" t="s">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s">
+        <v>237</v>
+      </c>
+      <c r="H70" t="s">
+        <v>238</v>
+      </c>
+      <c r="I70" t="s">
+        <v>47</v>
+      </c>
+      <c r="L70" t="s">
+        <v>82</v>
+      </c>
+      <c r="O70" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15">
+      <c r="B71" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C71">
+        <v>1922757</v>
+      </c>
+      <c r="D71" t="s">
+        <v>239</v>
+      </c>
+      <c r="G71" t="s">
+        <v>240</v>
+      </c>
+      <c r="H71" t="s">
+        <v>241</v>
+      </c>
+      <c r="I71" t="s">
+        <v>47</v>
+      </c>
+      <c r="L71" t="s">
+        <v>242</v>
+      </c>
+      <c r="O71" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15">
+      <c r="B72" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C72">
+        <v>1923157</v>
+      </c>
+      <c r="D72" t="s">
+        <v>243</v>
+      </c>
+      <c r="G72" t="s">
+        <v>244</v>
+      </c>
+      <c r="H72" t="s">
+        <v>245</v>
+      </c>
+      <c r="I72" t="s">
+        <v>47</v>
+      </c>
+      <c r="L72" t="s">
+        <v>246</v>
+      </c>
+      <c r="O72" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15">
+      <c r="B73" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C73">
+        <v>1922745</v>
+      </c>
+      <c r="D73" t="s">
+        <v>140</v>
+      </c>
+      <c r="G73" t="s">
+        <v>247</v>
+      </c>
+      <c r="H73" t="s">
+        <v>248</v>
+      </c>
+      <c r="I73" t="s">
+        <v>47</v>
+      </c>
+      <c r="L73" t="s">
+        <v>142</v>
+      </c>
+      <c r="O73" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15">
+      <c r="B74" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C74">
+        <v>1922765</v>
+      </c>
+      <c r="D74" t="s">
+        <v>188</v>
+      </c>
+      <c r="G74" t="s">
+        <v>244</v>
+      </c>
+      <c r="H74" t="s">
+        <v>249</v>
+      </c>
+      <c r="I74" t="s">
+        <v>47</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="O74" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15">
+      <c r="B75" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C75">
+        <v>1923146</v>
+      </c>
+      <c r="D75" t="s">
+        <v>250</v>
+      </c>
+      <c r="G75" t="s">
+        <v>251</v>
+      </c>
+      <c r="H75" t="s">
+        <v>252</v>
+      </c>
+      <c r="I75" t="s">
+        <v>47</v>
+      </c>
+      <c r="L75" t="s">
+        <v>253</v>
+      </c>
+      <c r="O75" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15">
+      <c r="B76" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C76">
+        <v>1922877</v>
+      </c>
+      <c r="D76" t="s">
+        <v>254</v>
+      </c>
+      <c r="G76" t="s">
+        <v>255</v>
+      </c>
+      <c r="H76" t="s">
+        <v>256</v>
+      </c>
+      <c r="I76" t="s">
+        <v>47</v>
+      </c>
+      <c r="L76" t="s">
+        <v>257</v>
+      </c>
+      <c r="O76" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15">
+      <c r="B77" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C77">
+        <v>1922812</v>
+      </c>
+      <c r="D77" t="s">
+        <v>119</v>
+      </c>
+      <c r="G77" t="s">
+        <v>258</v>
+      </c>
+      <c r="H77" t="s">
+        <v>259</v>
+      </c>
+      <c r="I77" t="s">
+        <v>47</v>
+      </c>
+      <c r="L77" t="s">
+        <v>122</v>
+      </c>
+      <c r="O77" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="78" spans="2:15">
+      <c r="B78" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C78">
+        <v>1923082</v>
+      </c>
+      <c r="D78" t="s">
+        <v>260</v>
+      </c>
+      <c r="G78" t="s">
+        <v>261</v>
+      </c>
+      <c r="H78" t="s">
+        <v>262</v>
+      </c>
+      <c r="I78" t="s">
+        <v>47</v>
+      </c>
+      <c r="L78" t="s">
+        <v>263</v>
+      </c>
+      <c r="O78" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15">
+      <c r="B79" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C79">
+        <v>1922828</v>
+      </c>
+      <c r="D79" t="s">
+        <v>250</v>
+      </c>
+      <c r="G79" t="s">
+        <v>264</v>
+      </c>
+      <c r="H79" t="s">
+        <v>265</v>
+      </c>
+      <c r="I79" t="s">
+        <v>47</v>
+      </c>
+      <c r="L79" t="s">
+        <v>253</v>
+      </c>
+      <c r="O79" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="80" spans="2:15">
+      <c r="B80" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C80">
+        <v>1922905</v>
+      </c>
+      <c r="D80" t="s">
+        <v>80</v>
+      </c>
+      <c r="G80" t="s">
+        <v>266</v>
+      </c>
+      <c r="H80" t="s">
+        <v>267</v>
+      </c>
+      <c r="I80" t="s">
+        <v>47</v>
+      </c>
+      <c r="L80" t="s">
+        <v>82</v>
+      </c>
+      <c r="O80" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="81" spans="2:15">
+      <c r="B81" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C81">
+        <v>1922926</v>
+      </c>
+      <c r="D81" t="s">
+        <v>268</v>
+      </c>
+      <c r="G81" t="s">
+        <v>269</v>
+      </c>
+      <c r="H81" t="s">
+        <v>270</v>
+      </c>
+      <c r="I81" t="s">
+        <v>47</v>
+      </c>
+      <c r="L81" t="s">
+        <v>271</v>
+      </c>
+      <c r="O81" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="82" spans="2:15">
+      <c r="B82" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C82">
+        <v>1922875</v>
+      </c>
+      <c r="D82" t="s">
+        <v>254</v>
+      </c>
+      <c r="G82" t="s">
+        <v>272</v>
+      </c>
+      <c r="H82" t="s">
+        <v>273</v>
+      </c>
+      <c r="I82" t="s">
+        <v>47</v>
+      </c>
+      <c r="L82" t="s">
+        <v>257</v>
+      </c>
+      <c r="O82" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="83" spans="2:15">
+      <c r="B83" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C83">
+        <v>1923126</v>
+      </c>
+      <c r="D83" t="s">
+        <v>250</v>
+      </c>
+      <c r="G83" t="s">
+        <v>274</v>
+      </c>
+      <c r="H83" t="s">
+        <v>275</v>
+      </c>
+      <c r="I83" t="s">
+        <v>47</v>
+      </c>
+      <c r="L83" t="s">
+        <v>253</v>
+      </c>
+      <c r="O83" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="84" spans="2:15">
+      <c r="B84" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C84">
+        <v>1922908</v>
+      </c>
+      <c r="D84" t="s">
+        <v>254</v>
+      </c>
+      <c r="G84" t="s">
+        <v>276</v>
+      </c>
+      <c r="H84" t="s">
+        <v>277</v>
+      </c>
+      <c r="I84" t="s">
+        <v>47</v>
+      </c>
+      <c r="L84" t="s">
+        <v>257</v>
+      </c>
+      <c r="O84" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="85" spans="2:15">
+      <c r="B85" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C85">
+        <v>1922987</v>
+      </c>
+      <c r="D85" t="s">
+        <v>185</v>
+      </c>
+      <c r="G85" t="s">
+        <v>278</v>
+      </c>
+      <c r="H85" t="s">
+        <v>279</v>
+      </c>
+      <c r="I85" t="s">
+        <v>47</v>
+      </c>
+      <c r="L85" t="s">
+        <v>187</v>
+      </c>
+      <c r="O85" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="86" spans="2:15">
+      <c r="B86" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C86">
+        <v>1922713</v>
+      </c>
+      <c r="D86" t="s">
+        <v>119</v>
+      </c>
+      <c r="G86" t="s">
+        <v>280</v>
+      </c>
+      <c r="H86" t="s">
+        <v>281</v>
+      </c>
+      <c r="I86" t="s">
+        <v>47</v>
+      </c>
+      <c r="L86" t="s">
+        <v>122</v>
+      </c>
+      <c r="O86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="87" spans="2:15">
+      <c r="B87" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C87">
+        <v>1923132</v>
+      </c>
+      <c r="D87" t="s">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s">
+        <v>282</v>
+      </c>
+      <c r="H87" t="s">
+        <v>283</v>
+      </c>
+      <c r="I87" t="s">
+        <v>47</v>
+      </c>
+      <c r="L87" t="s">
+        <v>82</v>
+      </c>
+      <c r="O87" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="88" spans="2:15">
+      <c r="B88" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C88">
+        <v>1923002</v>
+      </c>
+      <c r="D88" t="s">
+        <v>284</v>
+      </c>
+      <c r="G88" t="s">
+        <v>285</v>
+      </c>
+      <c r="H88" t="s">
+        <v>286</v>
+      </c>
+      <c r="I88" t="s">
+        <v>47</v>
+      </c>
+      <c r="L88" t="s">
+        <v>287</v>
+      </c>
+      <c r="O88" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="89" spans="2:15">
+      <c r="B89" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C89">
+        <v>1922695</v>
+      </c>
+      <c r="D89" t="s">
+        <v>119</v>
+      </c>
+      <c r="G89" t="s">
+        <v>288</v>
+      </c>
+      <c r="H89" t="s">
+        <v>289</v>
+      </c>
+      <c r="I89" t="s">
+        <v>47</v>
+      </c>
+      <c r="L89" t="s">
+        <v>122</v>
+      </c>
+      <c r="O89" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="90" spans="2:15">
+      <c r="B90" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C90">
+        <v>1922918</v>
+      </c>
+      <c r="D90" t="s">
+        <v>216</v>
+      </c>
+      <c r="G90" t="s">
+        <v>290</v>
+      </c>
+      <c r="H90" t="s">
+        <v>291</v>
+      </c>
+      <c r="I90" t="s">
+        <v>47</v>
+      </c>
+      <c r="L90" t="s">
+        <v>218</v>
+      </c>
+      <c r="O90" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="91" spans="2:15">
+      <c r="B91" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C91">
+        <v>1922863</v>
+      </c>
+      <c r="D91" t="s">
+        <v>292</v>
+      </c>
+      <c r="G91" t="s">
+        <v>293</v>
+      </c>
+      <c r="H91" t="s">
+        <v>294</v>
+      </c>
+      <c r="I91" t="s">
+        <v>47</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="O91" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="92" spans="2:15">
+      <c r="B92" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C92">
+        <v>1923000</v>
+      </c>
+      <c r="D92" t="s">
+        <v>295</v>
+      </c>
+      <c r="G92" t="s">
+        <v>296</v>
+      </c>
+      <c r="H92" t="s">
+        <v>297</v>
+      </c>
+      <c r="I92" t="s">
+        <v>47</v>
+      </c>
+      <c r="L92" t="s">
+        <v>298</v>
+      </c>
+      <c r="O92" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="93" spans="2:15">
+      <c r="B93" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C93">
+        <v>1922749</v>
+      </c>
+      <c r="D93" t="s">
+        <v>299</v>
+      </c>
+      <c r="G93" t="s">
+        <v>300</v>
+      </c>
+      <c r="H93" t="s">
+        <v>301</v>
+      </c>
+      <c r="I93" t="s">
+        <v>47</v>
+      </c>
+      <c r="L93" t="s">
+        <v>302</v>
+      </c>
+      <c r="O93" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="94" spans="2:15">
+      <c r="B94" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C94">
+        <v>1923144</v>
+      </c>
+      <c r="D94" t="s">
+        <v>250</v>
+      </c>
+      <c r="G94" t="s">
+        <v>303</v>
+      </c>
+      <c r="H94" t="s">
+        <v>304</v>
+      </c>
+      <c r="I94" t="s">
+        <v>47</v>
+      </c>
+      <c r="L94" t="s">
+        <v>253</v>
+      </c>
+      <c r="O94" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="95" spans="2:15">
+      <c r="B95" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C95">
+        <v>1923050</v>
+      </c>
+      <c r="D95" t="s">
+        <v>305</v>
+      </c>
+      <c r="G95" t="s">
+        <v>303</v>
+      </c>
+      <c r="H95" t="s">
+        <v>306</v>
+      </c>
+      <c r="I95" t="s">
+        <v>47</v>
+      </c>
+      <c r="L95" t="s">
+        <v>307</v>
+      </c>
+      <c r="O95" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="96" spans="2:15">
+      <c r="B96" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C96">
+        <v>1922954</v>
+      </c>
+      <c r="D96" t="s">
+        <v>299</v>
+      </c>
+      <c r="G96" t="s">
+        <v>308</v>
+      </c>
+      <c r="H96" t="s">
+        <v>309</v>
+      </c>
+      <c r="I96" t="s">
+        <v>47</v>
+      </c>
+      <c r="L96" t="s">
+        <v>302</v>
+      </c>
+      <c r="O96" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="97" spans="2:15">
+      <c r="B97" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C97">
+        <v>1922792</v>
+      </c>
+      <c r="D97" t="s">
+        <v>176</v>
+      </c>
+      <c r="G97" t="s">
+        <v>310</v>
+      </c>
+      <c r="H97" t="s">
+        <v>311</v>
+      </c>
+      <c r="I97" t="s">
+        <v>47</v>
+      </c>
+      <c r="L97" t="s">
+        <v>178</v>
+      </c>
+      <c r="O97" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="98" spans="2:15">
+      <c r="B98" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C98">
+        <v>1923148</v>
+      </c>
+      <c r="D98" t="s">
+        <v>188</v>
+      </c>
+      <c r="G98" t="s">
+        <v>312</v>
+      </c>
+      <c r="H98" t="s">
+        <v>313</v>
+      </c>
+      <c r="I98" t="s">
+        <v>47</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="O98" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="99" spans="2:15">
+      <c r="B99" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C99">
+        <v>1923139</v>
+      </c>
+      <c r="D99" t="s">
+        <v>185</v>
+      </c>
+      <c r="G99" t="s">
+        <v>314</v>
+      </c>
+      <c r="H99" t="s">
+        <v>315</v>
+      </c>
+      <c r="I99" t="s">
+        <v>47</v>
+      </c>
+      <c r="L99" t="s">
+        <v>187</v>
+      </c>
+      <c r="O99" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="100" spans="2:15">
+      <c r="B100" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C100">
+        <v>1923080</v>
+      </c>
+      <c r="D100" t="s">
+        <v>140</v>
+      </c>
+      <c r="G100" t="s">
+        <v>316</v>
+      </c>
+      <c r="H100" t="s">
+        <v>317</v>
+      </c>
+      <c r="I100" t="s">
+        <v>47</v>
+      </c>
+      <c r="L100" t="s">
+        <v>142</v>
+      </c>
+      <c r="O100" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="101" spans="2:15">
+      <c r="B101" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C101">
+        <v>1923072</v>
+      </c>
+      <c r="D101" t="s">
+        <v>83</v>
+      </c>
+      <c r="G101" t="s">
+        <v>318</v>
+      </c>
+      <c r="H101" t="s">
+        <v>319</v>
+      </c>
+      <c r="I101" t="s">
+        <v>47</v>
+      </c>
+      <c r="L101" t="s">
+        <v>86</v>
+      </c>
+      <c r="O101" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="102" spans="2:15">
+      <c r="B102" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C102">
+        <v>1923151</v>
+      </c>
+      <c r="D102" t="s">
+        <v>254</v>
+      </c>
+      <c r="G102" t="s">
+        <v>320</v>
+      </c>
+      <c r="H102" t="s">
+        <v>321</v>
+      </c>
+      <c r="I102" t="s">
+        <v>47</v>
+      </c>
+      <c r="L102" t="s">
+        <v>257</v>
+      </c>
+      <c r="O102" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="103" spans="2:15">
+      <c r="B103" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C103">
+        <v>1923141</v>
+      </c>
+      <c r="D103" t="s">
+        <v>250</v>
+      </c>
+      <c r="G103" t="s">
+        <v>322</v>
+      </c>
+      <c r="H103" t="s">
+        <v>323</v>
+      </c>
+      <c r="I103" t="s">
+        <v>47</v>
+      </c>
+      <c r="L103" t="s">
+        <v>253</v>
+      </c>
+      <c r="O103" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="104" spans="2:15">
+      <c r="B104" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C104">
+        <v>1922720</v>
+      </c>
+      <c r="D104" t="s">
+        <v>324</v>
+      </c>
+      <c r="G104" t="s">
+        <v>318</v>
+      </c>
+      <c r="H104" t="s">
+        <v>325</v>
+      </c>
+      <c r="I104" t="s">
+        <v>47</v>
+      </c>
+      <c r="L104" t="s">
+        <v>326</v>
+      </c>
+      <c r="O104" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="105" spans="2:15">
+      <c r="B105" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C105">
+        <v>1922924</v>
+      </c>
+      <c r="D105" t="s">
+        <v>73</v>
+      </c>
+      <c r="G105" t="s">
+        <v>327</v>
+      </c>
+      <c r="H105" t="s">
+        <v>328</v>
+      </c>
+      <c r="I105" t="s">
+        <v>47</v>
+      </c>
+      <c r="L105" t="s">
+        <v>75</v>
+      </c>
+      <c r="O105" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="106" spans="2:15">
+      <c r="B106" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C106">
+        <v>1922869</v>
+      </c>
+      <c r="D106" t="s">
+        <v>102</v>
+      </c>
+      <c r="G106" t="s">
+        <v>329</v>
+      </c>
+      <c r="H106" t="s">
+        <v>330</v>
+      </c>
+      <c r="I106" t="s">
+        <v>47</v>
+      </c>
+      <c r="L106" t="s">
+        <v>105</v>
+      </c>
+      <c r="O106" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="107" spans="2:15">
+      <c r="B107" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C107">
+        <v>1922836</v>
+      </c>
+      <c r="D107" t="s">
+        <v>140</v>
+      </c>
+      <c r="G107" t="s">
+        <v>331</v>
+      </c>
+      <c r="H107" t="s">
+        <v>332</v>
+      </c>
+      <c r="I107" t="s">
+        <v>47</v>
+      </c>
+      <c r="L107" t="s">
+        <v>142</v>
+      </c>
+      <c r="O107" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="108" spans="2:15">
+      <c r="B108" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C108">
+        <v>1922896</v>
+      </c>
+      <c r="D108" t="s">
+        <v>333</v>
+      </c>
+      <c r="G108" t="s">
+        <v>334</v>
+      </c>
+      <c r="H108" t="s">
+        <v>335</v>
+      </c>
+      <c r="I108" t="s">
+        <v>47</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="O108" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="109" spans="2:15">
+      <c r="B109" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C109">
+        <v>1923118</v>
+      </c>
+      <c r="D109" t="s">
+        <v>268</v>
+      </c>
+      <c r="G109" t="s">
+        <v>336</v>
+      </c>
+      <c r="H109" t="s">
+        <v>337</v>
+      </c>
+      <c r="I109" t="s">
+        <v>47</v>
+      </c>
+      <c r="L109" t="s">
+        <v>271</v>
+      </c>
+      <c r="O109" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="110" spans="2:15">
+      <c r="B110" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C110">
+        <v>1923056</v>
+      </c>
+      <c r="D110" t="s">
+        <v>305</v>
+      </c>
+      <c r="G110" t="s">
+        <v>336</v>
+      </c>
+      <c r="H110" t="s">
+        <v>338</v>
+      </c>
+      <c r="I110" t="s">
+        <v>47</v>
+      </c>
+      <c r="L110" t="s">
+        <v>307</v>
+      </c>
+      <c r="O110" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="111" spans="2:15">
+      <c r="B111" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C111">
+        <v>1922959</v>
+      </c>
+      <c r="D111" t="s">
+        <v>123</v>
+      </c>
+      <c r="G111" t="s">
+        <v>336</v>
+      </c>
+      <c r="H111" t="s">
+        <v>339</v>
+      </c>
+      <c r="I111" t="s">
+        <v>47</v>
+      </c>
+      <c r="L111" t="s">
+        <v>125</v>
+      </c>
+      <c r="O111" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="112" spans="2:15">
+      <c r="B112" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C112">
+        <v>1922755</v>
+      </c>
+      <c r="D112" t="s">
+        <v>284</v>
+      </c>
+      <c r="G112" t="s">
+        <v>340</v>
+      </c>
+      <c r="H112" t="s">
+        <v>341</v>
+      </c>
+      <c r="I112" t="s">
+        <v>47</v>
+      </c>
+      <c r="L112" t="s">
+        <v>287</v>
+      </c>
+      <c r="O112" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="113" spans="2:15">
+      <c r="B113" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C113">
+        <v>1922816</v>
+      </c>
+      <c r="D113" t="s">
+        <v>342</v>
+      </c>
+      <c r="G113" t="s">
+        <v>343</v>
+      </c>
+      <c r="H113" t="s">
+        <v>344</v>
+      </c>
+      <c r="I113" t="s">
+        <v>47</v>
+      </c>
+      <c r="L113" t="s">
+        <v>75</v>
+      </c>
+      <c r="O113" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="114" spans="2:15">
+      <c r="B114" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C114">
+        <v>1922751</v>
+      </c>
+      <c r="D114" t="s">
+        <v>299</v>
+      </c>
+      <c r="G114" t="s">
+        <v>318</v>
+      </c>
+      <c r="H114" t="s">
+        <v>345</v>
+      </c>
+      <c r="I114" t="s">
+        <v>47</v>
+      </c>
+      <c r="L114" t="s">
+        <v>302</v>
+      </c>
+      <c r="O114" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="115" spans="2:15">
+      <c r="B115" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C115">
+        <v>1922971</v>
+      </c>
+      <c r="D115" t="s">
+        <v>229</v>
+      </c>
+      <c r="G115" t="s">
+        <v>346</v>
+      </c>
+      <c r="H115" t="s">
+        <v>347</v>
+      </c>
+      <c r="I115" t="s">
+        <v>47</v>
+      </c>
+      <c r="L115" t="s">
+        <v>232</v>
+      </c>
+      <c r="O115" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="116" spans="2:15">
+      <c r="B116" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C116">
+        <v>1923128</v>
+      </c>
+      <c r="D116" t="s">
+        <v>250</v>
+      </c>
+      <c r="G116" t="s">
+        <v>348</v>
+      </c>
+      <c r="H116" t="s">
+        <v>349</v>
+      </c>
+      <c r="I116" t="s">
+        <v>47</v>
+      </c>
+      <c r="L116" t="s">
+        <v>253</v>
+      </c>
+      <c r="O116" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="117" spans="2:15">
+      <c r="B117" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C117">
+        <v>1922912</v>
+      </c>
+      <c r="D117" t="s">
+        <v>229</v>
+      </c>
+      <c r="G117" t="s">
+        <v>350</v>
+      </c>
+      <c r="H117" t="s">
+        <v>351</v>
+      </c>
+      <c r="I117" t="s">
+        <v>47</v>
+      </c>
+      <c r="L117" t="s">
+        <v>232</v>
+      </c>
+      <c r="O117" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="118" spans="2:15">
+      <c r="B118" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C118">
+        <v>1923102</v>
+      </c>
+      <c r="D118" t="s">
+        <v>106</v>
+      </c>
+      <c r="G118" t="s">
+        <v>352</v>
+      </c>
+      <c r="H118" t="s">
+        <v>353</v>
+      </c>
+      <c r="I118" t="s">
+        <v>47</v>
+      </c>
+      <c r="L118" t="s">
+        <v>109</v>
+      </c>
+      <c r="O118" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="119" spans="2:15">
+      <c r="B119" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C119">
+        <v>1922814</v>
+      </c>
+      <c r="D119" t="s">
+        <v>342</v>
+      </c>
+      <c r="G119" t="s">
+        <v>57</v>
+      </c>
+      <c r="H119" t="s">
+        <v>354</v>
+      </c>
+      <c r="I119" t="s">
+        <v>47</v>
+      </c>
+      <c r="L119" t="s">
+        <v>75</v>
+      </c>
+      <c r="O119" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="120" spans="2:15">
+      <c r="B120" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C120">
+        <v>1922732</v>
+      </c>
+      <c r="D120" t="s">
+        <v>207</v>
+      </c>
+      <c r="G120" t="s">
+        <v>355</v>
+      </c>
+      <c r="H120" t="s">
+        <v>356</v>
+      </c>
+      <c r="I120" t="s">
+        <v>47</v>
+      </c>
+      <c r="L120" t="s">
+        <v>209</v>
+      </c>
+      <c r="O120" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="121" spans="2:15">
+      <c r="B121" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C121">
+        <v>1923196</v>
+      </c>
+      <c r="D121" t="s">
+        <v>80</v>
+      </c>
+      <c r="G121" t="s">
+        <v>357</v>
+      </c>
+      <c r="H121" t="s">
+        <v>358</v>
+      </c>
+      <c r="I121" t="s">
+        <v>47</v>
+      </c>
+      <c r="L121" t="s">
+        <v>82</v>
+      </c>
+      <c r="O121" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="122" spans="2:15">
+      <c r="B122" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C122">
+        <v>1922932</v>
+      </c>
+      <c r="D122" t="s">
+        <v>223</v>
+      </c>
+      <c r="G122" t="s">
+        <v>359</v>
+      </c>
+      <c r="H122" t="s">
+        <v>360</v>
+      </c>
+      <c r="I122" t="s">
+        <v>47</v>
+      </c>
+      <c r="L122" t="s">
+        <v>225</v>
+      </c>
+      <c r="O122" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="123" spans="2:15">
+      <c r="B123" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C123">
+        <v>1922885</v>
+      </c>
+      <c r="D123" t="s">
+        <v>361</v>
+      </c>
+      <c r="G123" t="s">
+        <v>362</v>
+      </c>
+      <c r="H123" t="s">
+        <v>363</v>
+      </c>
+      <c r="I123" t="s">
+        <v>47</v>
+      </c>
+      <c r="L123" t="s">
+        <v>89</v>
+      </c>
+      <c r="O123" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="124" spans="2:15">
+      <c r="B124" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C124">
+        <v>1922788</v>
+      </c>
+      <c r="D124" t="s">
+        <v>126</v>
+      </c>
+      <c r="G124" t="s">
+        <v>364</v>
+      </c>
+      <c r="H124" t="s">
+        <v>365</v>
+      </c>
+      <c r="I124" t="s">
+        <v>47</v>
+      </c>
+      <c r="L124" t="s">
+        <v>129</v>
+      </c>
+      <c r="O124" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="125" spans="2:15">
+      <c r="B125" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C125">
+        <v>1922826</v>
+      </c>
+      <c r="D125" t="s">
+        <v>250</v>
+      </c>
+      <c r="G125" t="s">
+        <v>366</v>
+      </c>
+      <c r="H125" t="s">
+        <v>367</v>
+      </c>
+      <c r="I125" t="s">
+        <v>47</v>
+      </c>
+      <c r="L125" t="s">
+        <v>253</v>
+      </c>
+      <c r="O125" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="126" spans="2:15">
+      <c r="B126" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C126">
+        <v>1922705</v>
+      </c>
+      <c r="D126" t="s">
+        <v>56</v>
+      </c>
+      <c r="G126" t="s">
+        <v>368</v>
+      </c>
+      <c r="H126" t="s">
+        <v>369</v>
+      </c>
+      <c r="I126" t="s">
+        <v>47</v>
+      </c>
+      <c r="L126" t="s">
+        <v>59</v>
+      </c>
+      <c r="O126" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="127" spans="2:15">
+      <c r="B127" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C127">
+        <v>1923149</v>
+      </c>
+      <c r="D127" t="s">
+        <v>188</v>
+      </c>
+      <c r="G127" t="s">
+        <v>368</v>
+      </c>
+      <c r="H127" t="s">
+        <v>370</v>
+      </c>
+      <c r="I127" t="s">
+        <v>47</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="O127" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="128" spans="2:15">
+      <c r="B128" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C128">
+        <v>1923165</v>
+      </c>
+      <c r="D128" t="s">
+        <v>119</v>
+      </c>
+      <c r="G128" t="s">
+        <v>371</v>
+      </c>
+      <c r="H128" t="s">
+        <v>372</v>
+      </c>
+      <c r="I128" t="s">
+        <v>47</v>
+      </c>
+      <c r="L128" t="s">
+        <v>122</v>
+      </c>
+      <c r="O128" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="129" spans="2:15">
+      <c r="B129" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C129">
+        <v>1922942</v>
+      </c>
+      <c r="D129" t="s">
+        <v>254</v>
+      </c>
+      <c r="G129" t="s">
+        <v>371</v>
+      </c>
+      <c r="H129" t="s">
+        <v>373</v>
+      </c>
+      <c r="I129" t="s">
+        <v>47</v>
+      </c>
+      <c r="L129" t="s">
+        <v>257</v>
+      </c>
+      <c r="O129" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="130" spans="2:15">
+      <c r="B130" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C130">
+        <v>1922856</v>
+      </c>
+      <c r="D130" t="s">
+        <v>133</v>
+      </c>
+      <c r="G130" t="s">
+        <v>374</v>
+      </c>
+      <c r="H130" t="s">
+        <v>375</v>
+      </c>
+      <c r="I130" t="s">
+        <v>47</v>
+      </c>
+      <c r="L130" t="s">
+        <v>135</v>
+      </c>
+      <c r="O130" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="131" spans="2:15">
+      <c r="B131" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C131">
+        <v>1922747</v>
+      </c>
+      <c r="D131" t="s">
+        <v>239</v>
+      </c>
+      <c r="G131" t="s">
+        <v>376</v>
+      </c>
+      <c r="H131" t="s">
+        <v>377</v>
+      </c>
+      <c r="I131" t="s">
+        <v>47</v>
+      </c>
+      <c r="L131" t="s">
+        <v>242</v>
+      </c>
+      <c r="O131" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="132" spans="2:15">
+      <c r="B132" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C132">
+        <v>1923027</v>
+      </c>
+      <c r="D132" t="s">
+        <v>254</v>
+      </c>
+      <c r="G132" t="s">
+        <v>378</v>
+      </c>
+      <c r="H132" t="s">
+        <v>379</v>
+      </c>
+      <c r="I132" t="s">
+        <v>47</v>
+      </c>
+      <c r="L132" t="s">
+        <v>257</v>
+      </c>
+      <c r="O132" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="133" spans="2:15">
+      <c r="B133" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C133">
+        <v>1922753</v>
+      </c>
+      <c r="D133" t="s">
+        <v>239</v>
+      </c>
+      <c r="G133" t="s">
+        <v>380</v>
+      </c>
+      <c r="H133" t="s">
+        <v>381</v>
+      </c>
+      <c r="I133" t="s">
+        <v>47</v>
+      </c>
+      <c r="L133" t="s">
+        <v>242</v>
+      </c>
+      <c r="O133" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="134" spans="2:15">
+      <c r="B134" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C134">
+        <v>1923143</v>
+      </c>
+      <c r="D134" t="s">
+        <v>188</v>
+      </c>
+      <c r="G134" t="s">
+        <v>382</v>
+      </c>
+      <c r="H134" t="s">
+        <v>383</v>
+      </c>
+      <c r="I134" t="s">
+        <v>47</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="O134" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="135" spans="2:15">
+      <c r="B135" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C135">
+        <v>1922920</v>
+      </c>
+      <c r="D135" t="s">
+        <v>216</v>
+      </c>
+      <c r="G135" t="s">
+        <v>384</v>
+      </c>
+      <c r="H135" t="s">
+        <v>385</v>
+      </c>
+      <c r="I135" t="s">
+        <v>47</v>
+      </c>
+      <c r="L135" t="s">
+        <v>218</v>
+      </c>
+      <c r="O135" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="136" spans="2:15">
+      <c r="B136" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C136">
+        <v>1922967</v>
+      </c>
+      <c r="D136" t="s">
+        <v>216</v>
+      </c>
+      <c r="G136" t="s">
+        <v>386</v>
+      </c>
+      <c r="H136" t="s">
+        <v>387</v>
+      </c>
+      <c r="I136" t="s">
+        <v>47</v>
+      </c>
+      <c r="L136" t="s">
+        <v>218</v>
+      </c>
+      <c r="O136" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="137" spans="2:15">
+      <c r="B137" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C137">
+        <v>1922824</v>
+      </c>
+      <c r="D137" t="s">
+        <v>181</v>
+      </c>
+      <c r="G137" t="s">
+        <v>388</v>
+      </c>
+      <c r="H137" t="s">
+        <v>389</v>
+      </c>
+      <c r="I137" t="s">
+        <v>47</v>
+      </c>
+      <c r="L137" t="s">
+        <v>183</v>
+      </c>
+      <c r="O137" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="138" spans="2:15">
+      <c r="B138" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C138">
+        <v>1922687</v>
+      </c>
+      <c r="D138" t="s">
+        <v>166</v>
+      </c>
+      <c r="G138" t="s">
+        <v>390</v>
+      </c>
+      <c r="H138" t="s">
+        <v>391</v>
+      </c>
+      <c r="I138" t="s">
+        <v>47</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="O138" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="139" spans="2:15">
+      <c r="B139" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C139">
+        <v>1923063</v>
+      </c>
+      <c r="D139" t="s">
+        <v>392</v>
+      </c>
+      <c r="G139" t="s">
+        <v>393</v>
+      </c>
+      <c r="H139" t="s">
+        <v>394</v>
+      </c>
+      <c r="I139" t="s">
+        <v>47</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="O139" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="140" spans="2:15">
+      <c r="B140" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C140">
+        <v>1922850</v>
+      </c>
+      <c r="D140" t="s">
+        <v>239</v>
+      </c>
+      <c r="G140" t="s">
+        <v>395</v>
+      </c>
+      <c r="H140" t="s">
+        <v>396</v>
+      </c>
+      <c r="I140" t="s">
+        <v>47</v>
+      </c>
+      <c r="L140" t="s">
+        <v>242</v>
+      </c>
+      <c r="O140" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="141" spans="2:15">
+      <c r="B141" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C141">
+        <v>1923178</v>
+      </c>
+      <c r="D141" t="s">
+        <v>299</v>
+      </c>
+      <c r="G141" t="s">
+        <v>397</v>
+      </c>
+      <c r="H141" t="s">
+        <v>398</v>
+      </c>
+      <c r="I141" t="s">
+        <v>47</v>
+      </c>
+      <c r="L141" t="s">
+        <v>302</v>
+      </c>
+      <c r="O141" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="142" spans="2:15">
+      <c r="B142" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C142">
+        <v>1923040</v>
+      </c>
+      <c r="D142" t="s">
+        <v>254</v>
+      </c>
+      <c r="G142" t="s">
+        <v>399</v>
+      </c>
+      <c r="H142" t="s">
+        <v>400</v>
+      </c>
+      <c r="I142" t="s">
+        <v>47</v>
+      </c>
+      <c r="L142" t="s">
+        <v>257</v>
+      </c>
+      <c r="O142" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="143" spans="2:15">
+      <c r="B143" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C143">
+        <v>1923095</v>
+      </c>
+      <c r="D143" t="s">
+        <v>254</v>
+      </c>
+      <c r="G143" t="s">
+        <v>401</v>
+      </c>
+      <c r="H143" t="s">
+        <v>402</v>
+      </c>
+      <c r="I143" t="s">
+        <v>47</v>
+      </c>
+      <c r="L143" t="s">
+        <v>257</v>
+      </c>
+      <c r="O143" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="144" spans="2:15">
+      <c r="B144" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C144">
+        <v>1922797</v>
+      </c>
+      <c r="D144" t="s">
+        <v>147</v>
+      </c>
+      <c r="G144" t="s">
+        <v>403</v>
+      </c>
+      <c r="H144" t="s">
+        <v>404</v>
+      </c>
+      <c r="I144" t="s">
+        <v>47</v>
+      </c>
+      <c r="L144" t="s">
+        <v>150</v>
+      </c>
+      <c r="O144" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="145" spans="2:15">
+      <c r="B145" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C145">
+        <v>1923052</v>
+      </c>
+      <c r="D145" t="s">
+        <v>254</v>
+      </c>
+      <c r="G145" t="s">
+        <v>405</v>
+      </c>
+      <c r="H145" t="s">
+        <v>406</v>
+      </c>
+      <c r="I145" t="s">
+        <v>47</v>
+      </c>
+      <c r="L145" t="s">
+        <v>257</v>
+      </c>
+      <c r="O145" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="146" spans="2:15">
+      <c r="B146" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C146">
+        <v>1922776</v>
+      </c>
+      <c r="D146" t="s">
+        <v>407</v>
+      </c>
+      <c r="G146" t="s">
+        <v>408</v>
+      </c>
+      <c r="H146" t="s">
+        <v>409</v>
+      </c>
+      <c r="I146" t="s">
+        <v>47</v>
+      </c>
+      <c r="L146" t="s">
+        <v>209</v>
+      </c>
+      <c r="O146" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="147" spans="2:15">
+      <c r="B147" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C147">
+        <v>1922907</v>
+      </c>
+      <c r="D147" t="s">
+        <v>410</v>
+      </c>
+      <c r="G147" t="s">
+        <v>411</v>
+      </c>
+      <c r="H147" t="s">
+        <v>412</v>
+      </c>
+      <c r="I147" t="s">
+        <v>47</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="O147" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="148" spans="2:15">
+      <c r="B148" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C148">
+        <v>1922867</v>
+      </c>
+      <c r="D148" t="s">
+        <v>102</v>
+      </c>
+      <c r="G148" t="s">
+        <v>413</v>
+      </c>
+      <c r="H148" t="s">
+        <v>414</v>
+      </c>
+      <c r="I148" t="s">
+        <v>47</v>
+      </c>
+      <c r="L148" t="s">
+        <v>105</v>
+      </c>
+      <c r="O148" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="149" spans="2:15">
+      <c r="B149" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C149">
+        <v>1922780</v>
+      </c>
+      <c r="D149" t="s">
+        <v>415</v>
+      </c>
+      <c r="G149" t="s">
+        <v>416</v>
+      </c>
+      <c r="H149" t="s">
+        <v>417</v>
+      </c>
+      <c r="I149" t="s">
+        <v>47</v>
+      </c>
+      <c r="L149" t="s">
+        <v>418</v>
+      </c>
+      <c r="O149" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="150" spans="2:15">
+      <c r="B150" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C150">
+        <v>1923035</v>
+      </c>
+      <c r="D150" t="s">
+        <v>254</v>
+      </c>
+      <c r="G150" t="s">
+        <v>419</v>
+      </c>
+      <c r="H150" t="s">
+        <v>420</v>
+      </c>
+      <c r="I150" t="s">
+        <v>47</v>
+      </c>
+      <c r="L150" t="s">
+        <v>257</v>
+      </c>
+      <c r="O150" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="151" spans="2:15">
+      <c r="B151" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C151">
+        <v>1922988</v>
+      </c>
+      <c r="D151" t="s">
+        <v>421</v>
+      </c>
+      <c r="F151" t="s">
+        <v>422</v>
+      </c>
+      <c r="H151" t="s">
+        <v>423</v>
+      </c>
+      <c r="I151" t="s">
+        <v>47</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="O151" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="152" spans="2:15">
+      <c r="B152" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C152">
+        <v>1922737</v>
+      </c>
+      <c r="D152" t="s">
+        <v>424</v>
+      </c>
+      <c r="G152" t="s">
+        <v>425</v>
+      </c>
+      <c r="H152" t="s">
+        <v>426</v>
+      </c>
+      <c r="I152" t="s">
+        <v>47</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="O152" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="153" spans="2:15">
+      <c r="B153" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C153">
+        <v>1923060</v>
+      </c>
+      <c r="D153" t="s">
+        <v>223</v>
+      </c>
+      <c r="G153" t="s">
+        <v>427</v>
+      </c>
+      <c r="H153" t="s">
+        <v>428</v>
+      </c>
+      <c r="I153" t="s">
+        <v>47</v>
+      </c>
+      <c r="L153" t="s">
+        <v>225</v>
+      </c>
+      <c r="O153" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="154" spans="2:15">
+      <c r="B154" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C154">
+        <v>1922832</v>
+      </c>
+      <c r="D154" t="s">
+        <v>250</v>
+      </c>
+      <c r="G154" t="s">
+        <v>427</v>
+      </c>
+      <c r="H154" t="s">
+        <v>429</v>
+      </c>
+      <c r="I154" t="s">
+        <v>47</v>
+      </c>
+      <c r="L154" t="s">
+        <v>253</v>
+      </c>
+      <c r="O154" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="155" spans="2:15">
+      <c r="B155" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C155">
+        <v>1922961</v>
+      </c>
+      <c r="D155" t="s">
+        <v>207</v>
+      </c>
+      <c r="G155" t="s">
+        <v>430</v>
+      </c>
+      <c r="H155" t="s">
+        <v>431</v>
+      </c>
+      <c r="I155" t="s">
+        <v>47</v>
+      </c>
+      <c r="L155" t="s">
+        <v>209</v>
+      </c>
+      <c r="O155" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="156" spans="2:15">
+      <c r="B156" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C156">
+        <v>1922922</v>
+      </c>
+      <c r="D156" t="s">
+        <v>119</v>
+      </c>
+      <c r="G156" t="s">
+        <v>432</v>
+      </c>
+      <c r="H156" t="s">
+        <v>433</v>
+      </c>
+      <c r="I156" t="s">
+        <v>47</v>
+      </c>
+      <c r="L156" t="s">
+        <v>122</v>
+      </c>
+      <c r="O156" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="157" spans="2:15">
+      <c r="B157" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C157">
+        <v>1922874</v>
+      </c>
+      <c r="D157" t="s">
+        <v>434</v>
+      </c>
+      <c r="F157" t="s">
+        <v>435</v>
+      </c>
+      <c r="H157" t="s">
+        <v>436</v>
+      </c>
+      <c r="I157" t="s">
+        <v>47</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="O157" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="158" spans="2:15">
+      <c r="B158" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C158">
+        <v>1922820</v>
+      </c>
+      <c r="D158" t="s">
+        <v>181</v>
+      </c>
+      <c r="G158" t="s">
+        <v>437</v>
+      </c>
+      <c r="H158" t="s">
+        <v>438</v>
+      </c>
+      <c r="I158" t="s">
+        <v>47</v>
+      </c>
+      <c r="L158" t="s">
+        <v>183</v>
+      </c>
+      <c r="O158" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="159" spans="2:15">
+      <c r="B159" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C159">
+        <v>1923150</v>
+      </c>
+      <c r="D159" t="s">
+        <v>188</v>
+      </c>
+      <c r="G159" t="s">
+        <v>437</v>
+      </c>
+      <c r="H159" t="s">
+        <v>439</v>
+      </c>
+      <c r="I159" t="s">
+        <v>47</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
+      <c r="O159" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="160" spans="2:15">
+      <c r="B160" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C160">
+        <v>1923078</v>
+      </c>
+      <c r="D160" t="s">
+        <v>87</v>
+      </c>
+      <c r="G160" t="s">
+        <v>440</v>
+      </c>
+      <c r="H160" t="s">
+        <v>441</v>
+      </c>
+      <c r="I160" t="s">
+        <v>47</v>
+      </c>
+      <c r="L160" t="s">
+        <v>89</v>
+      </c>
+      <c r="O160" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="161" spans="2:15">
+      <c r="B161" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C161">
+        <v>1922889</v>
+      </c>
+      <c r="D161" t="s">
+        <v>424</v>
+      </c>
+      <c r="G161" t="s">
+        <v>442</v>
+      </c>
+      <c r="H161" t="s">
+        <v>443</v>
+      </c>
+      <c r="I161" t="s">
+        <v>47</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+      <c r="O161" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="162" spans="2:15">
+      <c r="B162" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C162">
+        <v>1922973</v>
+      </c>
+      <c r="D162" t="s">
+        <v>207</v>
+      </c>
+      <c r="G162" t="s">
+        <v>444</v>
+      </c>
+      <c r="H162" t="s">
+        <v>445</v>
+      </c>
+      <c r="I162" t="s">
+        <v>47</v>
+      </c>
+      <c r="L162" t="s">
+        <v>209</v>
+      </c>
+      <c r="O162" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="163" spans="2:15">
+      <c r="B163" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C163">
+        <v>1922916</v>
+      </c>
+      <c r="D163" t="s">
+        <v>119</v>
+      </c>
+      <c r="G163" t="s">
+        <v>446</v>
+      </c>
+      <c r="H163" t="s">
+        <v>447</v>
+      </c>
+      <c r="I163" t="s">
+        <v>47</v>
+      </c>
+      <c r="L163" t="s">
+        <v>122</v>
+      </c>
+      <c r="O163" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="164" spans="2:15">
+      <c r="B164" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C164">
+        <v>1922871</v>
+      </c>
+      <c r="D164" t="s">
+        <v>448</v>
+      </c>
+      <c r="G164" t="s">
+        <v>449</v>
+      </c>
+      <c r="H164" t="s">
+        <v>450</v>
+      </c>
+      <c r="I164" t="s">
+        <v>47</v>
+      </c>
+      <c r="L164" t="s">
+        <v>109</v>
+      </c>
+      <c r="O164" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="165" spans="2:15">
+      <c r="B165" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C165">
+        <v>1922873</v>
+      </c>
+      <c r="D165" t="s">
+        <v>243</v>
+      </c>
+      <c r="G165" t="s">
+        <v>451</v>
+      </c>
+      <c r="H165" t="s">
+        <v>452</v>
+      </c>
+      <c r="I165" t="s">
+        <v>47</v>
+      </c>
+      <c r="L165" t="s">
+        <v>246</v>
+      </c>
+      <c r="O165" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="166" spans="2:15">
+      <c r="B166" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C166">
+        <v>1922818</v>
+      </c>
+      <c r="D166" t="s">
+        <v>181</v>
+      </c>
+      <c r="G166" t="s">
+        <v>453</v>
+      </c>
+      <c r="H166" t="s">
+        <v>454</v>
+      </c>
+      <c r="I166" t="s">
+        <v>47</v>
+      </c>
+      <c r="L166" t="s">
+        <v>183</v>
+      </c>
+      <c r="O166" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="167" spans="2:15">
+      <c r="B167" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C167">
+        <v>1922709</v>
+      </c>
+      <c r="D167" t="s">
+        <v>455</v>
+      </c>
+      <c r="G167" t="s">
+        <v>456</v>
+      </c>
+      <c r="H167" t="s">
+        <v>457</v>
+      </c>
+      <c r="I167" t="s">
+        <v>47</v>
+      </c>
+      <c r="L167" t="s">
+        <v>458</v>
+      </c>
+      <c r="O167" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="168" spans="2:15">
+      <c r="B168" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C168">
+        <v>1922722</v>
+      </c>
+      <c r="D168" t="s">
+        <v>117</v>
+      </c>
+      <c r="G168" t="s">
+        <v>459</v>
+      </c>
+      <c r="H168" t="s">
+        <v>460</v>
+      </c>
+      <c r="I168" t="s">
+        <v>47</v>
+      </c>
+      <c r="L168" t="s">
+        <v>86</v>
+      </c>
+      <c r="O168" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="169" spans="2:15">
+      <c r="B169" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C169">
+        <v>1922691</v>
+      </c>
+      <c r="D169" t="s">
+        <v>143</v>
+      </c>
+      <c r="G169" t="s">
+        <v>461</v>
+      </c>
+      <c r="H169" t="s">
+        <v>462</v>
+      </c>
+      <c r="I169" t="s">
+        <v>47</v>
+      </c>
+      <c r="L169" t="s">
+        <v>146</v>
+      </c>
+      <c r="O169" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="170" spans="2:15">
+      <c r="B170" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C170">
+        <v>1922754</v>
+      </c>
+      <c r="D170" t="s">
+        <v>421</v>
+      </c>
+      <c r="F170" t="s">
+        <v>463</v>
+      </c>
+      <c r="H170" t="s">
+        <v>464</v>
+      </c>
+      <c r="I170" t="s">
+        <v>47</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="O170" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="171" spans="2:15">
+      <c r="B171" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C171">
+        <v>1922853</v>
+      </c>
+      <c r="D171" t="s">
+        <v>465</v>
+      </c>
+      <c r="F171" t="s">
+        <v>466</v>
+      </c>
+      <c r="H171" t="s">
+        <v>467</v>
+      </c>
+      <c r="I171" t="s">
+        <v>47</v>
+      </c>
+      <c r="L171" t="s">
+        <v>468</v>
+      </c>
+      <c r="O171" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="172" spans="2:15">
+      <c r="B172" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C172">
+        <v>1922835</v>
+      </c>
+      <c r="D172" t="s">
+        <v>465</v>
+      </c>
+      <c r="F172" t="s">
+        <v>469</v>
+      </c>
+      <c r="H172" t="s">
+        <v>470</v>
+      </c>
+      <c r="I172" t="s">
+        <v>47</v>
+      </c>
+      <c r="L172" t="s">
+        <v>468</v>
+      </c>
+      <c r="O172" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="173" spans="2:15">
+      <c r="B173" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C173">
+        <v>1923195</v>
+      </c>
+      <c r="D173" t="s">
+        <v>471</v>
+      </c>
+      <c r="F173" t="s">
+        <v>472</v>
+      </c>
+      <c r="H173" t="s">
+        <v>473</v>
+      </c>
+      <c r="I173" t="s">
+        <v>47</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="O173" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="174" spans="2:15">
+      <c r="B174" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C174">
+        <v>1923062</v>
+      </c>
+      <c r="D174" t="s">
+        <v>474</v>
+      </c>
+      <c r="F174" t="s">
+        <v>393</v>
+      </c>
+      <c r="H174" t="s">
+        <v>475</v>
+      </c>
+      <c r="I174" t="s">
+        <v>47</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+      <c r="O174" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="175" spans="2:15">
+      <c r="B175" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C175">
+        <v>1922760</v>
+      </c>
+      <c r="D175" t="s">
+        <v>465</v>
+      </c>
+      <c r="F175" t="s">
+        <v>476</v>
+      </c>
+      <c r="H175" t="s">
+        <v>477</v>
+      </c>
+      <c r="I175" t="s">
+        <v>47</v>
+      </c>
+      <c r="L175" t="s">
+        <v>468</v>
+      </c>
+      <c r="O175" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="176" spans="2:15">
+      <c r="B176" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C176">
+        <v>1923064</v>
+      </c>
+      <c r="D176" t="s">
+        <v>478</v>
+      </c>
+      <c r="F176" t="s">
+        <v>479</v>
+      </c>
+      <c r="H176" t="s">
+        <v>480</v>
+      </c>
+      <c r="I176" t="s">
+        <v>47</v>
+      </c>
+      <c r="L176">
+        <v>0</v>
+      </c>
+      <c r="O176" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="177" spans="2:15">
+      <c r="B177" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C177">
+        <v>1922953</v>
+      </c>
+      <c r="D177" t="s">
+        <v>465</v>
+      </c>
+      <c r="F177" t="s">
+        <v>481</v>
+      </c>
+      <c r="H177" t="s">
+        <v>482</v>
+      </c>
+      <c r="I177" t="s">
+        <v>47</v>
+      </c>
+      <c r="L177" t="s">
+        <v>468</v>
+      </c>
+      <c r="O177" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="178" spans="2:15">
+      <c r="B178" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C178">
+        <v>1922834</v>
+      </c>
+      <c r="D178" t="s">
+        <v>483</v>
+      </c>
+      <c r="F178" t="s">
+        <v>484</v>
+      </c>
+      <c r="H178" t="s">
+        <v>485</v>
+      </c>
+      <c r="I178" t="s">
+        <v>47</v>
+      </c>
+      <c r="L178">
+        <v>0</v>
+      </c>
+      <c r="O178" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="179" spans="2:15">
+      <c r="B179" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C179">
+        <v>1923194</v>
+      </c>
+      <c r="D179" t="s">
+        <v>486</v>
+      </c>
+      <c r="F179" t="s">
+        <v>487</v>
+      </c>
+      <c r="H179" t="s">
+        <v>488</v>
+      </c>
+      <c r="I179" t="s">
+        <v>47</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+      <c r="O179" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="180" spans="2:15">
+      <c r="B180" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C180">
+        <v>1922783</v>
+      </c>
+      <c r="D180" t="s">
+        <v>465</v>
+      </c>
+      <c r="F180" t="s">
+        <v>489</v>
+      </c>
+      <c r="H180" t="s">
+        <v>490</v>
+      </c>
+      <c r="I180" t="s">
+        <v>47</v>
+      </c>
+      <c r="L180" t="s">
+        <v>468</v>
+      </c>
+      <c r="O180" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="181" spans="2:15">
+      <c r="B181" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C181">
+        <v>1922865</v>
+      </c>
+      <c r="D181" t="s">
+        <v>465</v>
+      </c>
+      <c r="F181" t="s">
+        <v>491</v>
+      </c>
+      <c r="H181" t="s">
+        <v>492</v>
+      </c>
+      <c r="I181" t="s">
+        <v>47</v>
+      </c>
+      <c r="L181" t="s">
+        <v>468</v>
+      </c>
+      <c r="O181" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="182" spans="2:15">
+      <c r="B182" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C182">
+        <v>1922900</v>
+      </c>
+      <c r="D182" t="s">
+        <v>465</v>
+      </c>
+      <c r="F182" t="s">
+        <v>493</v>
+      </c>
+      <c r="H182" t="s">
+        <v>494</v>
+      </c>
+      <c r="I182" t="s">
+        <v>47</v>
+      </c>
+      <c r="L182" t="s">
+        <v>468</v>
+      </c>
+      <c r="O182" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="183" spans="2:15">
+      <c r="B183" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C183">
+        <v>1922740</v>
+      </c>
+      <c r="D183" t="s">
+        <v>465</v>
+      </c>
+      <c r="F183" t="s">
+        <v>495</v>
+      </c>
+      <c r="H183" t="s">
+        <v>496</v>
+      </c>
+      <c r="I183" t="s">
+        <v>47</v>
+      </c>
+      <c r="L183" t="s">
+        <v>468</v>
+      </c>
+      <c r="O183" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="184" spans="2:15">
+      <c r="B184" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C184">
+        <v>1922915</v>
+      </c>
+      <c r="D184" t="s">
+        <v>465</v>
+      </c>
+      <c r="F184" t="s">
+        <v>497</v>
+      </c>
+      <c r="H184" t="s">
+        <v>498</v>
+      </c>
+      <c r="I184" t="s">
+        <v>47</v>
+      </c>
+      <c r="L184" t="s">
+        <v>468</v>
+      </c>
+      <c r="O184" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="185" spans="2:15">
+      <c r="B185" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C185">
+        <v>1922859</v>
+      </c>
+      <c r="D185" t="s">
+        <v>465</v>
+      </c>
+      <c r="F185" t="s">
+        <v>499</v>
+      </c>
+      <c r="H185" t="s">
+        <v>500</v>
+      </c>
+      <c r="I185" t="s">
+        <v>47</v>
+      </c>
+      <c r="L185" t="s">
+        <v>468</v>
+      </c>
+      <c r="O185" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="186" spans="2:15">
+      <c r="B186" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C186">
+        <v>1922763</v>
+      </c>
+      <c r="D186" t="s">
+        <v>465</v>
+      </c>
+      <c r="F186" t="s">
+        <v>501</v>
+      </c>
+      <c r="H186" t="s">
+        <v>502</v>
+      </c>
+      <c r="I186" t="s">
+        <v>47</v>
+      </c>
+      <c r="L186" t="s">
+        <v>468</v>
+      </c>
+      <c r="O186" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="187" spans="2:15">
+      <c r="B187" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C187">
+        <v>1922948</v>
+      </c>
+      <c r="D187" t="s">
+        <v>465</v>
+      </c>
+      <c r="F187" t="s">
+        <v>503</v>
+      </c>
+      <c r="H187" t="s">
+        <v>504</v>
+      </c>
+      <c r="I187" t="s">
+        <v>47</v>
+      </c>
+      <c r="L187" t="s">
+        <v>468</v>
+      </c>
+      <c r="O187" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="188" spans="2:15">
+      <c r="B188" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C188">
+        <v>1922712</v>
+      </c>
+      <c r="D188" t="s">
+        <v>465</v>
+      </c>
+      <c r="F188" t="s">
+        <v>505</v>
+      </c>
+      <c r="H188" t="s">
+        <v>506</v>
+      </c>
+      <c r="I188" t="s">
+        <v>47</v>
+      </c>
+      <c r="L188" t="s">
+        <v>468</v>
+      </c>
+      <c r="O188" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="189" spans="2:15">
+      <c r="B189" s="10">
+        <v>46099</v>
+      </c>
+      <c r="C189">
+        <v>1923059</v>
+      </c>
+      <c r="D189" t="s">
+        <v>465</v>
+      </c>
+      <c r="F189" t="s">
+        <v>507</v>
+      </c>
+      <c r="H189" t="s">
+        <v>508</v>
+      </c>
+      <c r="I189" t="s">
+        <v>47</v>
+      </c>
+      <c r="L189" t="s">
+        <v>468</v>
+      </c>
+      <c r="O189" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="190" spans="2:15">
+      <c r="B190" s="10">
+        <v>46099</v>
+      </c>
+      <c r="H190" t="s">
+        <v>508</v>
+      </c>
+      <c r="I190" t="s">
+        <v>47</v>
+      </c>
+      <c r="O190" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.2"/>
